--- a/inputs/diccionario.xlsx
+++ b/inputs/diccionario.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\eaneg\OneDrive\Desktop\Datos TP\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Eugenio\Maestria\Series Temporales\series_temporales_2025\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54443985-89BE-4325-9678-F940C7FFB768}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40425F3B-61C8-4E68-BDFD-0DA4A9752E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="85">
   <si>
     <t>fecha</t>
   </si>
@@ -252,15 +252,60 @@
   <si>
     <t>UVA</t>
   </si>
+  <si>
+    <t>m1</t>
+  </si>
+  <si>
+    <t>Agregado monetario que comprende, en la Argentina, circulante en poder del público más cuentas corrientes en pesos del sector público y privado no financiero. </t>
+  </si>
+  <si>
+    <t>m2</t>
+  </si>
+  <si>
+    <t>Medios de pago, comprende circulante en poder del público más depósitos a la vista en pesos del sector público y privado no financiero. </t>
+  </si>
+  <si>
+    <t>m3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Agregado monetario amplio, comprende circulante en poder del público más total de depósitos en pesos del sector público y privado no financiero. </t>
+  </si>
+  <si>
+    <t>inflacion</t>
+  </si>
+  <si>
+    <t>Tasa de variación mensual</t>
+  </si>
+  <si>
+    <t>Elaboracion propia en base a BCRA</t>
+  </si>
+  <si>
+    <t>Inflación mensual</t>
+  </si>
+  <si>
+    <t>rem</t>
+  </si>
+  <si>
+    <t>Inflación esperada - REM próximos 12 meses - MEDIANA (variación en i.a)</t>
+  </si>
+  <si>
+    <t>Tasa de variación anual</t>
+  </si>
+  <si>
+    <t>prestamos_privados_en_pesos_ars</t>
+  </si>
+  <si>
+    <t>Stock de prestamos en pesos al sector privado</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="172" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="164" formatCode="yyyy\-mm\-dd;@"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -272,6 +317,12 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -298,16 +349,17 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="172" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -17544,7 +17596,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68D9661-D5F8-4698-9487-A24691442B2A}">
-  <dimension ref="A1:E25"/>
+  <dimension ref="A1:E31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
@@ -17977,6 +18029,108 @@
         <v>46</v>
       </c>
     </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>70</v>
+      </c>
+      <c r="B26" t="s">
+        <v>59</v>
+      </c>
+      <c r="C26" t="s">
+        <v>20</v>
+      </c>
+      <c r="D26" t="s">
+        <v>71</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>72</v>
+      </c>
+      <c r="B27" t="s">
+        <v>59</v>
+      </c>
+      <c r="C27" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" t="s">
+        <v>73</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>74</v>
+      </c>
+      <c r="B28" t="s">
+        <v>59</v>
+      </c>
+      <c r="C28" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" t="s">
+        <v>75</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>76</v>
+      </c>
+      <c r="B29" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29" t="s">
+        <v>79</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B30" t="s">
+        <v>82</v>
+      </c>
+      <c r="C30" t="s">
+        <v>25</v>
+      </c>
+      <c r="D30" t="s">
+        <v>81</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>83</v>
+      </c>
+      <c r="B31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C31" t="s">
+        <v>20</v>
+      </c>
+      <c r="D31" t="s">
+        <v>84</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>46</v>
+      </c>
+    </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1" xr:uid="{367FD9AC-ED1F-4BF3-8464-A874C9BF1185}"/>
@@ -17985,6 +18139,9 @@
     <hyperlink ref="E9" r:id="rId4" xr:uid="{570D3B3F-B1C2-4459-A684-E7EE4C8EA780}"/>
     <hyperlink ref="E8" r:id="rId5" xr:uid="{AADE2B87-8679-4A1A-AFD1-91980FA8EC08}"/>
     <hyperlink ref="E7" r:id="rId6" xr:uid="{0574CB13-C3FA-4963-9589-C7E5AD7B791E}"/>
+    <hyperlink ref="E29" r:id="rId7" xr:uid="{C0365983-E341-4415-8B33-003D3D04E6BF}"/>
+    <hyperlink ref="E30" r:id="rId8" xr:uid="{FED48BAD-8C63-476A-80B7-A83938422758}"/>
+    <hyperlink ref="E31" r:id="rId9" xr:uid="{94DCFB4E-22E7-4981-BAE5-80A634946772}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/inputs/diccionario.xlsx
+++ b/inputs/diccionario.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Eugenio\Maestria\Series Temporales\series_temporales_2025\inputs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\i_link\Maestría\Series Temporales\tp\inputs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40425F3B-61C8-4E68-BDFD-0DA4A9752E49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DD12F4C-26E3-48C2-9C31-D635E99C8677}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -30,15 +30,12 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="86">
   <si>
     <t>fecha</t>
   </si>
@@ -292,10 +289,13 @@
     <t>Tasa de variación anual</t>
   </si>
   <si>
-    <t>prestamos_privados_en_pesos_ars</t>
+    <t>Stock de prestamos en pesos al sector privado</t>
   </si>
   <si>
-    <t>Stock de prestamos en pesos al sector privado</t>
+    <t>m2_transaccional</t>
+  </si>
+  <si>
+    <t>prestamos_privados_pesos_ars</t>
   </si>
 </sst>
 </file>
@@ -328,12 +328,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -349,20 +355,19 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+    <cellStyle name="Hipervínculo" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -642,13 +647,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Y232"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.7265625" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -725,8 +730,8 @@
         <v>45</v>
       </c>
     </row>
-    <row r="2" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A2" s="3">
         <v>45566</v>
       </c>
       <c r="B2">
@@ -747,7 +752,7 @@
       <c r="G2">
         <v>147.99752842547727</v>
       </c>
-      <c r="H2" s="3">
+      <c r="H2">
         <v>149.06594071044972</v>
       </c>
       <c r="I2">
@@ -792,7 +797,7 @@
       <c r="V2">
         <v>45186941</v>
       </c>
-      <c r="W2" s="5">
+      <c r="W2" s="4">
         <v>35</v>
       </c>
       <c r="X2">
@@ -802,8 +807,8 @@
         <v>1185.22</v>
       </c>
     </row>
-    <row r="3" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A3" s="3">
         <v>45567</v>
       </c>
       <c r="B3">
@@ -824,7 +829,7 @@
       <c r="G3">
         <v>147.99752842547727</v>
       </c>
-      <c r="H3" s="3">
+      <c r="H3">
         <v>149.06594071044972</v>
       </c>
       <c r="I3">
@@ -869,7 +874,7 @@
       <c r="V3">
         <v>45187714</v>
       </c>
-      <c r="W3" s="5">
+      <c r="W3" s="4">
         <v>35</v>
       </c>
       <c r="X3">
@@ -879,8 +884,8 @@
         <v>1186.8499999999999</v>
       </c>
     </row>
-    <row r="4" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A4" s="3">
         <v>45568</v>
       </c>
       <c r="B4">
@@ -901,7 +906,7 @@
       <c r="G4">
         <v>147.99752842547727</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4">
         <v>149.06594071044972</v>
       </c>
       <c r="I4">
@@ -946,7 +951,7 @@
       <c r="V4">
         <v>45268430</v>
       </c>
-      <c r="W4" s="5">
+      <c r="W4" s="4">
         <v>35</v>
       </c>
       <c r="X4">
@@ -956,8 +961,8 @@
         <v>1188.48</v>
       </c>
     </row>
-    <row r="5" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A5" s="3">
         <v>45569</v>
       </c>
       <c r="B5">
@@ -978,7 +983,7 @@
       <c r="G5">
         <v>147.99752842547727</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5">
         <v>149.06594071044972</v>
       </c>
       <c r="I5">
@@ -1023,7 +1028,7 @@
       <c r="V5">
         <v>45031409</v>
       </c>
-      <c r="W5" s="5">
+      <c r="W5" s="4">
         <v>35</v>
       </c>
       <c r="X5">
@@ -1033,8 +1038,8 @@
         <v>1190.1099999999999</v>
       </c>
     </row>
-    <row r="6" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A6" s="3">
         <v>45572</v>
       </c>
       <c r="B6">
@@ -1055,7 +1060,7 @@
       <c r="G6">
         <v>147.99752842547727</v>
       </c>
-      <c r="H6" s="3">
+      <c r="H6">
         <v>149.06594071044972</v>
       </c>
       <c r="I6">
@@ -1100,7 +1105,7 @@
       <c r="V6">
         <v>44865592</v>
       </c>
-      <c r="W6" s="5">
+      <c r="W6" s="4">
         <v>35</v>
       </c>
       <c r="X6">
@@ -1110,8 +1115,8 @@
         <v>1191.74</v>
       </c>
     </row>
-    <row r="7" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A7" s="3">
         <v>45573</v>
       </c>
       <c r="B7">
@@ -1132,7 +1137,7 @@
       <c r="G7">
         <v>147.99752842547727</v>
       </c>
-      <c r="H7" s="3">
+      <c r="H7">
         <v>149.06594071044972</v>
       </c>
       <c r="I7">
@@ -1177,7 +1182,7 @@
       <c r="V7">
         <v>45051245</v>
       </c>
-      <c r="W7" s="5">
+      <c r="W7" s="4">
         <v>35</v>
       </c>
       <c r="X7">
@@ -1187,8 +1192,8 @@
         <v>1196.6500000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A8" s="3">
         <v>45574</v>
       </c>
       <c r="B8">
@@ -1209,7 +1214,7 @@
       <c r="G8">
         <v>147.99752842547727</v>
       </c>
-      <c r="H8" s="3">
+      <c r="H8">
         <v>149.06594071044972</v>
       </c>
       <c r="I8">
@@ -1254,7 +1259,7 @@
       <c r="V8">
         <v>45197611</v>
       </c>
-      <c r="W8" s="5">
+      <c r="W8" s="4">
         <v>35</v>
       </c>
       <c r="X8">
@@ -1264,8 +1269,8 @@
         <v>1198.3</v>
       </c>
     </row>
-    <row r="9" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A9" s="3">
         <v>45575</v>
       </c>
       <c r="B9">
@@ -1286,7 +1291,7 @@
       <c r="G9">
         <v>147.99752842547727</v>
       </c>
-      <c r="H9" s="3">
+      <c r="H9">
         <v>149.06594071044972</v>
       </c>
       <c r="I9">
@@ -1331,7 +1336,7 @@
       <c r="V9">
         <v>45821403</v>
       </c>
-      <c r="W9" s="5">
+      <c r="W9" s="4">
         <v>35</v>
       </c>
       <c r="X9">
@@ -1341,8 +1346,8 @@
         <v>1199.94</v>
       </c>
     </row>
-    <row r="10" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A10" s="3">
         <v>45579</v>
       </c>
       <c r="B10">
@@ -1354,7 +1359,7 @@
       <c r="G10">
         <v>147.99752842547727</v>
       </c>
-      <c r="H10" s="3">
+      <c r="H10">
         <v>149.06594071044972</v>
       </c>
       <c r="I10">
@@ -1399,7 +1404,7 @@
       <c r="V10">
         <v>45734171</v>
       </c>
-      <c r="W10" s="5">
+      <c r="W10" s="4">
         <v>35</v>
       </c>
       <c r="X10">
@@ -1409,8 +1414,8 @@
         <v>1201.5899999999999</v>
       </c>
     </row>
-    <row r="11" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A11" s="3">
         <v>45580</v>
       </c>
       <c r="B11">
@@ -1431,7 +1436,7 @@
       <c r="G11">
         <v>147.99752842547727</v>
       </c>
-      <c r="H11" s="3">
+      <c r="H11">
         <v>149.06594071044972</v>
       </c>
       <c r="I11">
@@ -1476,7 +1481,7 @@
       <c r="V11">
         <v>46979485</v>
       </c>
-      <c r="W11" s="5">
+      <c r="W11" s="4">
         <v>35</v>
       </c>
       <c r="X11">
@@ -1486,8 +1491,8 @@
         <v>1208.2</v>
       </c>
     </row>
-    <row r="12" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A12" s="3">
         <v>45581</v>
       </c>
       <c r="B12">
@@ -1508,7 +1513,7 @@
       <c r="G12">
         <v>147.99752842547727</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12">
         <v>149.06594071044972</v>
       </c>
       <c r="I12">
@@ -1553,7 +1558,7 @@
       <c r="V12">
         <v>47365496</v>
       </c>
-      <c r="W12" s="5">
+      <c r="W12" s="4">
         <v>35</v>
       </c>
       <c r="X12">
@@ -1563,8 +1568,8 @@
         <v>1209.8499999999999</v>
       </c>
     </row>
-    <row r="13" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A13" s="3">
         <v>45582</v>
       </c>
       <c r="B13">
@@ -1585,7 +1590,7 @@
       <c r="G13">
         <v>147.99752842547727</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13">
         <v>149.06594071044972</v>
       </c>
       <c r="I13">
@@ -1630,7 +1635,7 @@
       <c r="V13">
         <v>48095587</v>
       </c>
-      <c r="W13" s="5">
+      <c r="W13" s="4">
         <v>35</v>
       </c>
       <c r="X13">
@@ -1640,8 +1645,8 @@
         <v>1211.2</v>
       </c>
     </row>
-    <row r="14" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A14" s="3">
         <v>45583</v>
       </c>
       <c r="B14">
@@ -1662,7 +1667,7 @@
       <c r="G14">
         <v>147.99752842547727</v>
       </c>
-      <c r="H14" s="3">
+      <c r="H14">
         <v>149.06594071044972</v>
       </c>
       <c r="I14">
@@ -1707,7 +1712,7 @@
       <c r="V14">
         <v>49065778</v>
       </c>
-      <c r="W14" s="5">
+      <c r="W14" s="4">
         <v>35</v>
       </c>
       <c r="X14">
@@ -1717,8 +1722,8 @@
         <v>1212.54</v>
       </c>
     </row>
-    <row r="15" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A15" s="3">
         <v>45586</v>
       </c>
       <c r="B15">
@@ -1739,7 +1744,7 @@
       <c r="G15">
         <v>147.99752842547727</v>
       </c>
-      <c r="H15" s="3">
+      <c r="H15">
         <v>149.06594071044972</v>
       </c>
       <c r="I15">
@@ -1784,7 +1789,7 @@
       <c r="V15">
         <v>48793758</v>
       </c>
-      <c r="W15" s="5">
+      <c r="W15" s="4">
         <v>35</v>
       </c>
       <c r="X15">
@@ -1794,8 +1799,8 @@
         <v>1213.8900000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A16" s="3">
         <v>45587</v>
       </c>
       <c r="B16">
@@ -1816,7 +1821,7 @@
       <c r="G16">
         <v>147.99752842547727</v>
       </c>
-      <c r="H16" s="3">
+      <c r="H16">
         <v>149.06594071044972</v>
       </c>
       <c r="I16">
@@ -1861,7 +1866,7 @@
       <c r="V16">
         <v>49421794</v>
       </c>
-      <c r="W16" s="5">
+      <c r="W16" s="4">
         <v>35</v>
       </c>
       <c r="X16">
@@ -1871,8 +1876,8 @@
         <v>1217.94</v>
       </c>
     </row>
-    <row r="17" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
+    <row r="17" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A17" s="3">
         <v>45588</v>
       </c>
       <c r="B17">
@@ -1893,7 +1898,7 @@
       <c r="G17">
         <v>147.99752842547727</v>
       </c>
-      <c r="H17" s="3">
+      <c r="H17">
         <v>149.06594071044972</v>
       </c>
       <c r="I17">
@@ -1938,7 +1943,7 @@
       <c r="V17">
         <v>49356014</v>
       </c>
-      <c r="W17" s="5">
+      <c r="W17" s="4">
         <v>35</v>
       </c>
       <c r="X17">
@@ -1948,8 +1953,8 @@
         <v>1219.29</v>
       </c>
     </row>
-    <row r="18" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
+    <row r="18" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A18" s="3">
         <v>45589</v>
       </c>
       <c r="B18">
@@ -1970,7 +1975,7 @@
       <c r="G18">
         <v>147.99752842547727</v>
       </c>
-      <c r="H18" s="3">
+      <c r="H18">
         <v>149.06594071044972</v>
       </c>
       <c r="I18">
@@ -2015,7 +2020,7 @@
       <c r="V18">
         <v>49578016</v>
       </c>
-      <c r="W18" s="5">
+      <c r="W18" s="4">
         <v>35</v>
       </c>
       <c r="X18">
@@ -2025,8 +2030,8 @@
         <v>1220.6400000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
+    <row r="19" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A19" s="3">
         <v>45590</v>
       </c>
       <c r="B19">
@@ -2047,7 +2052,7 @@
       <c r="G19">
         <v>147.99752842547727</v>
       </c>
-      <c r="H19" s="3">
+      <c r="H19">
         <v>149.06594071044972</v>
       </c>
       <c r="I19">
@@ -2092,7 +2097,7 @@
       <c r="V19">
         <v>50319180</v>
       </c>
-      <c r="W19" s="5">
+      <c r="W19" s="4">
         <v>35</v>
       </c>
       <c r="X19">
@@ -2102,8 +2107,8 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="20" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
+    <row r="20" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A20" s="3">
         <v>45593</v>
       </c>
       <c r="B20">
@@ -2124,7 +2129,7 @@
       <c r="G20">
         <v>147.99752842547727</v>
       </c>
-      <c r="H20" s="3">
+      <c r="H20">
         <v>149.06594071044972</v>
       </c>
       <c r="I20">
@@ -2169,7 +2174,7 @@
       <c r="V20">
         <v>49472640</v>
       </c>
-      <c r="W20" s="5">
+      <c r="W20" s="4">
         <v>35</v>
       </c>
       <c r="X20">
@@ -2179,8 +2184,8 @@
         <v>1223.3599999999999</v>
       </c>
     </row>
-    <row r="21" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
+    <row r="21" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A21" s="3">
         <v>45594</v>
       </c>
       <c r="B21">
@@ -2201,7 +2206,7 @@
       <c r="G21">
         <v>147.99752842547727</v>
       </c>
-      <c r="H21" s="3">
+      <c r="H21">
         <v>149.06594071044972</v>
       </c>
       <c r="I21">
@@ -2246,7 +2251,7 @@
       <c r="V21">
         <v>49617649</v>
       </c>
-      <c r="W21" s="5">
+      <c r="W21" s="4">
         <v>35</v>
       </c>
       <c r="X21">
@@ -2256,8 +2261,8 @@
         <v>1227.43</v>
       </c>
     </row>
-    <row r="22" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
+    <row r="22" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A22" s="3">
         <v>45595</v>
       </c>
       <c r="B22">
@@ -2278,7 +2283,7 @@
       <c r="G22">
         <v>147.99752842547727</v>
       </c>
-      <c r="H22" s="3">
+      <c r="H22">
         <v>149.06594071044972</v>
       </c>
       <c r="I22">
@@ -2323,7 +2328,7 @@
       <c r="V22">
         <v>49166279</v>
       </c>
-      <c r="W22" s="5">
+      <c r="W22" s="4">
         <v>35</v>
       </c>
       <c r="X22">
@@ -2333,8 +2338,8 @@
         <v>1228.8</v>
       </c>
     </row>
-    <row r="23" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A23" s="4">
+    <row r="23" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A23" s="3">
         <v>45596</v>
       </c>
       <c r="B23">
@@ -2355,7 +2360,7 @@
       <c r="G23">
         <v>147.99752842547727</v>
       </c>
-      <c r="H23" s="3">
+      <c r="H23">
         <v>149.06594071044972</v>
       </c>
       <c r="I23">
@@ -2400,7 +2405,7 @@
       <c r="V23">
         <v>48569336</v>
       </c>
-      <c r="W23" s="5">
+      <c r="W23" s="4">
         <v>35</v>
       </c>
       <c r="X23">
@@ -2410,8 +2415,8 @@
         <v>1230.1600000000001</v>
       </c>
     </row>
-    <row r="24" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A24" s="4">
+    <row r="24" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A24" s="3">
         <v>45597</v>
       </c>
       <c r="B24">
@@ -2432,7 +2437,7 @@
       <c r="G24">
         <v>148.07058297356372</v>
       </c>
-      <c r="H24" s="3">
+      <c r="H24">
         <v>150.62871014356878</v>
       </c>
       <c r="I24">
@@ -2477,7 +2482,7 @@
       <c r="V24">
         <v>48899290</v>
       </c>
-      <c r="W24" s="5">
+      <c r="W24" s="4">
         <v>29.4</v>
       </c>
       <c r="X24">
@@ -2487,8 +2492,8 @@
         <v>1231.53</v>
       </c>
     </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A25" s="4">
+    <row r="25" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A25" s="3">
         <v>45600</v>
       </c>
       <c r="B25">
@@ -2509,7 +2514,7 @@
       <c r="G25">
         <v>148.07058297356372</v>
       </c>
-      <c r="H25" s="3">
+      <c r="H25">
         <v>150.62871014356878</v>
       </c>
       <c r="I25">
@@ -2554,7 +2559,7 @@
       <c r="V25">
         <v>48968208</v>
       </c>
-      <c r="W25" s="5">
+      <c r="W25" s="4">
         <v>29.4</v>
       </c>
       <c r="X25">
@@ -2564,8 +2569,8 @@
         <v>1232.9000000000001</v>
       </c>
     </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A26" s="4">
+    <row r="26" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A26" s="3">
         <v>45601</v>
       </c>
       <c r="B26">
@@ -2586,7 +2591,7 @@
       <c r="G26">
         <v>148.07058297356372</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <v>150.62871014356878</v>
       </c>
       <c r="I26">
@@ -2631,7 +2636,7 @@
       <c r="V26">
         <v>48897842</v>
       </c>
-      <c r="W26" s="5">
+      <c r="W26" s="4">
         <v>29.4</v>
       </c>
       <c r="X26">
@@ -2641,8 +2646,8 @@
         <v>1237.01</v>
       </c>
     </row>
-    <row r="27" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A27" s="4">
+    <row r="27" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A27" s="3">
         <v>45602</v>
       </c>
       <c r="B27">
@@ -2663,16 +2668,13 @@
       <c r="G27">
         <v>148.07058297356372</v>
       </c>
-      <c r="H27" s="3">
+      <c r="H27">
         <v>150.62871014356878</v>
       </c>
       <c r="I27">
         <v>149.11470443517911</v>
       </c>
-      <c r="J27" s="6"/>
-      <c r="K27" s="6"/>
-      <c r="L27" s="6"/>
-      <c r="W27" s="5">
+      <c r="W27" s="4">
         <v>29.4</v>
       </c>
       <c r="X27">
@@ -2682,8 +2684,8 @@
         <v>1238.3800000000001</v>
       </c>
     </row>
-    <row r="28" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A28" s="4">
+    <row r="28" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A28" s="3">
         <v>45603</v>
       </c>
       <c r="B28">
@@ -2704,7 +2706,7 @@
       <c r="G28">
         <v>148.07058297356372</v>
       </c>
-      <c r="H28" s="3">
+      <c r="H28">
         <v>150.62871014356878</v>
       </c>
       <c r="I28">
@@ -2749,7 +2751,7 @@
       <c r="V28">
         <v>48739395</v>
       </c>
-      <c r="W28" s="5">
+      <c r="W28" s="4">
         <v>29.4</v>
       </c>
       <c r="X28">
@@ -2759,8 +2761,8 @@
         <v>1238.3800000000001</v>
       </c>
     </row>
-    <row r="29" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A29" s="4">
+    <row r="29" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A29" s="3">
         <v>45604</v>
       </c>
       <c r="B29">
@@ -2781,7 +2783,7 @@
       <c r="G29">
         <v>148.07058297356372</v>
       </c>
-      <c r="H29" s="3">
+      <c r="H29">
         <v>150.62871014356878</v>
       </c>
       <c r="I29">
@@ -2826,7 +2828,7 @@
       <c r="V29">
         <v>49119100</v>
       </c>
-      <c r="W29" s="5">
+      <c r="W29" s="4">
         <v>29.4</v>
       </c>
       <c r="X29">
@@ -2836,8 +2838,8 @@
         <v>1241.1300000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A30" s="4">
+    <row r="30" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A30" s="3">
         <v>45607</v>
       </c>
       <c r="B30">
@@ -2849,7 +2851,7 @@
       <c r="G30">
         <v>148.07058297356372</v>
       </c>
-      <c r="H30" s="3">
+      <c r="H30">
         <v>150.62871014356878</v>
       </c>
       <c r="I30">
@@ -2894,7 +2896,7 @@
       <c r="V30">
         <v>49169206</v>
       </c>
-      <c r="W30" s="5">
+      <c r="W30" s="4">
         <v>29.4</v>
       </c>
       <c r="X30">
@@ -2904,8 +2906,8 @@
         <v>1242.51</v>
       </c>
     </row>
-    <row r="31" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A31" s="4">
+    <row r="31" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A31" s="3">
         <v>45608</v>
       </c>
       <c r="B31">
@@ -2926,7 +2928,7 @@
       <c r="G31">
         <v>148.07058297356372</v>
       </c>
-      <c r="H31" s="3">
+      <c r="H31">
         <v>150.62871014356878</v>
       </c>
       <c r="I31">
@@ -2971,7 +2973,7 @@
       <c r="V31">
         <v>50314189</v>
       </c>
-      <c r="W31" s="5">
+      <c r="W31" s="4">
         <v>29.4</v>
       </c>
       <c r="X31">
@@ -2981,8 +2983,8 @@
         <v>1246.6500000000001</v>
       </c>
     </row>
-    <row r="32" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A32" s="4">
+    <row r="32" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A32" s="3">
         <v>45609</v>
       </c>
       <c r="B32">
@@ -3003,7 +3005,7 @@
       <c r="G32">
         <v>148.07058297356372</v>
       </c>
-      <c r="H32" s="3">
+      <c r="H32">
         <v>150.62871014356878</v>
       </c>
       <c r="I32">
@@ -3048,7 +3050,7 @@
       <c r="V32">
         <v>50421472</v>
       </c>
-      <c r="W32" s="5">
+      <c r="W32" s="4">
         <v>29.4</v>
       </c>
       <c r="X32">
@@ -3058,8 +3060,8 @@
         <v>1248.04</v>
       </c>
     </row>
-    <row r="33" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A33" s="4">
+    <row r="33" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A33" s="3">
         <v>45610</v>
       </c>
       <c r="B33">
@@ -3080,7 +3082,7 @@
       <c r="G33">
         <v>148.07058297356372</v>
       </c>
-      <c r="H33" s="3">
+      <c r="H33">
         <v>150.62871014356878</v>
       </c>
       <c r="I33">
@@ -3125,7 +3127,7 @@
       <c r="V33">
         <v>51397584</v>
       </c>
-      <c r="W33" s="5">
+      <c r="W33" s="4">
         <v>29.4</v>
       </c>
       <c r="X33">
@@ -3135,8 +3137,8 @@
         <v>1249.42</v>
       </c>
     </row>
-    <row r="34" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A34" s="4">
+    <row r="34" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A34" s="3">
         <v>45611</v>
       </c>
       <c r="B34">
@@ -3157,7 +3159,7 @@
       <c r="G34">
         <v>148.07058297356372</v>
       </c>
-      <c r="H34" s="3">
+      <c r="H34">
         <v>150.62871014356878</v>
       </c>
       <c r="I34">
@@ -3202,7 +3204,7 @@
       <c r="V34">
         <v>52137769</v>
       </c>
-      <c r="W34" s="5">
+      <c r="W34" s="4">
         <v>29.4</v>
       </c>
       <c r="X34">
@@ -3212,8 +3214,8 @@
         <v>1250.81</v>
       </c>
     </row>
-    <row r="35" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A35" s="4">
+    <row r="35" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A35" s="3">
         <v>45615</v>
       </c>
       <c r="B35">
@@ -3234,7 +3236,7 @@
       <c r="G35">
         <v>148.07058297356372</v>
       </c>
-      <c r="H35" s="3">
+      <c r="H35">
         <v>150.62871014356878</v>
       </c>
       <c r="I35">
@@ -3279,7 +3281,7 @@
       <c r="V35">
         <v>51932422</v>
       </c>
-      <c r="W35" s="5">
+      <c r="W35" s="4">
         <v>29.4</v>
       </c>
       <c r="X35">
@@ -3289,8 +3291,8 @@
         <v>1252.2</v>
       </c>
     </row>
-    <row r="36" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A36" s="4">
+    <row r="36" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A36" s="3">
         <v>45616</v>
       </c>
       <c r="B36">
@@ -3311,7 +3313,7 @@
       <c r="G36">
         <v>148.07058297356372</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36">
         <v>150.62871014356878</v>
       </c>
       <c r="I36">
@@ -3356,7 +3358,7 @@
       <c r="V36">
         <v>52164864</v>
       </c>
-      <c r="W36" s="5">
+      <c r="W36" s="4">
         <v>29.4</v>
       </c>
       <c r="X36">
@@ -3366,8 +3368,8 @@
         <v>1256.6600000000001</v>
       </c>
     </row>
-    <row r="37" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A37" s="4">
+    <row r="37" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A37" s="3">
         <v>45617</v>
       </c>
       <c r="B37">
@@ -3388,7 +3390,7 @@
       <c r="G37">
         <v>148.07058297356372</v>
       </c>
-      <c r="H37" s="3">
+      <c r="H37">
         <v>150.62871014356878</v>
       </c>
       <c r="I37">
@@ -3433,7 +3435,7 @@
       <c r="V37">
         <v>52728465</v>
       </c>
-      <c r="W37" s="5">
+      <c r="W37" s="4">
         <v>29.4</v>
       </c>
       <c r="X37">
@@ -3443,8 +3445,8 @@
         <v>1257.77</v>
       </c>
     </row>
-    <row r="38" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A38" s="4">
+    <row r="38" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A38" s="3">
         <v>45618</v>
       </c>
       <c r="B38">
@@ -3465,7 +3467,7 @@
       <c r="G38">
         <v>148.07058297356372</v>
       </c>
-      <c r="H38" s="3">
+      <c r="H38">
         <v>150.62871014356878</v>
       </c>
       <c r="I38">
@@ -3510,7 +3512,7 @@
       <c r="V38">
         <v>52913716</v>
       </c>
-      <c r="W38" s="5">
+      <c r="W38" s="4">
         <v>29.4</v>
       </c>
       <c r="X38">
@@ -3520,8 +3522,8 @@
         <v>1258.8900000000001</v>
       </c>
     </row>
-    <row r="39" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A39" s="4">
+    <row r="39" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A39" s="3">
         <v>45621</v>
       </c>
       <c r="B39">
@@ -3542,7 +3544,7 @@
       <c r="G39">
         <v>148.07058297356372</v>
       </c>
-      <c r="H39" s="3">
+      <c r="H39">
         <v>150.62871014356878</v>
       </c>
       <c r="I39">
@@ -3587,7 +3589,7 @@
       <c r="V39">
         <v>52810775</v>
       </c>
-      <c r="W39" s="5">
+      <c r="W39" s="4">
         <v>29.4</v>
       </c>
       <c r="X39">
@@ -3597,8 +3599,8 @@
         <v>1260.01</v>
       </c>
     </row>
-    <row r="40" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A40" s="4">
+    <row r="40" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A40" s="3">
         <v>45622</v>
       </c>
       <c r="B40">
@@ -3619,7 +3621,7 @@
       <c r="G40">
         <v>148.07058297356372</v>
       </c>
-      <c r="H40" s="3">
+      <c r="H40">
         <v>150.62871014356878</v>
       </c>
       <c r="I40">
@@ -3664,7 +3666,7 @@
       <c r="V40">
         <v>53504061</v>
       </c>
-      <c r="W40" s="5">
+      <c r="W40" s="4">
         <v>29.4</v>
       </c>
       <c r="X40">
@@ -3674,8 +3676,8 @@
         <v>1263.3699999999999</v>
       </c>
     </row>
-    <row r="41" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A41" s="4">
+    <row r="41" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A41" s="3">
         <v>45623</v>
       </c>
       <c r="B41">
@@ -3696,7 +3698,7 @@
       <c r="G41">
         <v>148.07058297356372</v>
       </c>
-      <c r="H41" s="3">
+      <c r="H41">
         <v>150.62871014356878</v>
       </c>
       <c r="I41">
@@ -3741,7 +3743,7 @@
       <c r="V41">
         <v>52371332</v>
       </c>
-      <c r="W41" s="5">
+      <c r="W41" s="4">
         <v>29.4</v>
       </c>
       <c r="X41">
@@ -3751,8 +3753,8 @@
         <v>1264.49</v>
       </c>
     </row>
-    <row r="42" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A42" s="4">
+    <row r="42" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A42" s="3">
         <v>45624</v>
       </c>
       <c r="B42">
@@ -3764,7 +3766,7 @@
       <c r="G42">
         <v>148.07058297356372</v>
       </c>
-      <c r="H42" s="3">
+      <c r="H42">
         <v>150.62871014356878</v>
       </c>
       <c r="I42">
@@ -3809,7 +3811,7 @@
       <c r="V42">
         <v>52020296</v>
       </c>
-      <c r="W42" s="5">
+      <c r="W42" s="4">
         <v>29.4</v>
       </c>
       <c r="X42">
@@ -3819,8 +3821,8 @@
         <v>1265.6099999999999</v>
       </c>
     </row>
-    <row r="43" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A43" s="4">
+    <row r="43" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A43" s="3">
         <v>45625</v>
       </c>
       <c r="B43">
@@ -3841,7 +3843,7 @@
       <c r="G43">
         <v>148.07058297356372</v>
       </c>
-      <c r="H43" s="3">
+      <c r="H43">
         <v>150.62871014356878</v>
       </c>
       <c r="I43">
@@ -3886,7 +3888,7 @@
       <c r="V43">
         <v>52240721</v>
       </c>
-      <c r="W43" s="5">
+      <c r="W43" s="4">
         <v>29.4</v>
       </c>
       <c r="X43">
@@ -3896,8 +3898,8 @@
         <v>1266.74</v>
       </c>
     </row>
-    <row r="44" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A44" s="4">
+    <row r="44" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A44" s="3">
         <v>45628</v>
       </c>
       <c r="B44">
@@ -3918,7 +3920,7 @@
       <c r="G44">
         <v>148.56326772984039</v>
       </c>
-      <c r="H44" s="3">
+      <c r="H44">
         <v>152.35944846589911</v>
       </c>
       <c r="I44">
@@ -3963,7 +3965,7 @@
       <c r="V44">
         <v>52385066</v>
       </c>
-      <c r="W44" s="5">
+      <c r="W44" s="4">
         <v>25.9</v>
       </c>
       <c r="X44">
@@ -3973,8 +3975,8 @@
         <v>1267.8599999999999</v>
       </c>
     </row>
-    <row r="45" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A45" s="4">
+    <row r="45" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A45" s="3">
         <v>45629</v>
       </c>
       <c r="B45">
@@ -3995,7 +3997,7 @@
       <c r="G45">
         <v>148.56326772984039</v>
       </c>
-      <c r="H45" s="3">
+      <c r="H45">
         <v>152.35944846589911</v>
       </c>
       <c r="I45">
@@ -4040,7 +4042,7 @@
       <c r="V45">
         <v>52910769</v>
       </c>
-      <c r="W45" s="5">
+      <c r="W45" s="4">
         <v>25.9</v>
       </c>
       <c r="X45">
@@ -4050,8 +4052,8 @@
         <v>1271.25</v>
       </c>
     </row>
-    <row r="46" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A46" s="4">
+    <row r="46" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A46" s="3">
         <v>45630</v>
       </c>
       <c r="B46">
@@ -4072,7 +4074,7 @@
       <c r="G46">
         <v>148.56326772984039</v>
       </c>
-      <c r="H46" s="3">
+      <c r="H46">
         <v>152.35944846589911</v>
       </c>
       <c r="I46">
@@ -4117,7 +4119,7 @@
       <c r="V46">
         <v>52563264</v>
       </c>
-      <c r="W46" s="5">
+      <c r="W46" s="4">
         <v>25.9</v>
       </c>
       <c r="X46">
@@ -4127,8 +4129,8 @@
         <v>1272.3800000000001</v>
       </c>
     </row>
-    <row r="47" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A47" s="4">
+    <row r="47" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A47" s="3">
         <v>45631</v>
       </c>
       <c r="B47">
@@ -4149,7 +4151,7 @@
       <c r="G47">
         <v>148.56326772984039</v>
       </c>
-      <c r="H47" s="3">
+      <c r="H47">
         <v>152.35944846589911</v>
       </c>
       <c r="I47">
@@ -4194,7 +4196,7 @@
       <c r="V47">
         <v>52302753</v>
       </c>
-      <c r="W47" s="5">
+      <c r="W47" s="4">
         <v>25.9</v>
       </c>
       <c r="X47">
@@ -4204,8 +4206,8 @@
         <v>1273.51</v>
       </c>
     </row>
-    <row r="48" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A48" s="4">
+    <row r="48" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A48" s="3">
         <v>45632</v>
       </c>
       <c r="B48">
@@ -4226,7 +4228,7 @@
       <c r="G48">
         <v>148.56326772984039</v>
       </c>
-      <c r="H48" s="3">
+      <c r="H48">
         <v>152.35944846589911</v>
       </c>
       <c r="I48">
@@ -4271,7 +4273,7 @@
       <c r="V48">
         <v>52789035</v>
       </c>
-      <c r="W48" s="5">
+      <c r="W48" s="4">
         <v>25.9</v>
       </c>
       <c r="X48">
@@ -4281,8 +4283,8 @@
         <v>1274.6400000000001</v>
       </c>
     </row>
-    <row r="49" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A49" s="4">
+    <row r="49" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A49" s="3">
         <v>45635</v>
       </c>
       <c r="B49">
@@ -4303,7 +4305,7 @@
       <c r="G49">
         <v>148.56326772984039</v>
       </c>
-      <c r="H49" s="3">
+      <c r="H49">
         <v>152.35944846589911</v>
       </c>
       <c r="I49">
@@ -4348,7 +4350,7 @@
       <c r="V49">
         <v>51810593</v>
       </c>
-      <c r="W49" s="5">
+      <c r="W49" s="4">
         <v>25.9</v>
       </c>
       <c r="X49">
@@ -4358,8 +4360,8 @@
         <v>1275.77</v>
       </c>
     </row>
-    <row r="50" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A50" s="4">
+    <row r="50" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A50" s="3">
         <v>45636</v>
       </c>
       <c r="B50">
@@ -4380,7 +4382,7 @@
       <c r="G50">
         <v>148.56326772984039</v>
       </c>
-      <c r="H50" s="3">
+      <c r="H50">
         <v>152.35944846589911</v>
       </c>
       <c r="I50">
@@ -4425,7 +4427,7 @@
       <c r="V50">
         <v>52059828</v>
       </c>
-      <c r="W50" s="5">
+      <c r="W50" s="4">
         <v>25.9</v>
       </c>
       <c r="X50">
@@ -4435,8 +4437,8 @@
         <v>1279.17</v>
       </c>
     </row>
-    <row r="51" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A51" s="4">
+    <row r="51" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A51" s="3">
         <v>45637</v>
       </c>
       <c r="B51">
@@ -4457,7 +4459,7 @@
       <c r="G51">
         <v>148.56326772984039</v>
       </c>
-      <c r="H51" s="3">
+      <c r="H51">
         <v>152.35944846589911</v>
       </c>
       <c r="I51">
@@ -4502,7 +4504,7 @@
       <c r="V51">
         <v>52285905</v>
       </c>
-      <c r="W51" s="5">
+      <c r="W51" s="4">
         <v>25.9</v>
       </c>
       <c r="X51">
@@ -4512,8 +4514,8 @@
         <v>1280.31</v>
       </c>
     </row>
-    <row r="52" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A52" s="4">
+    <row r="52" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A52" s="3">
         <v>45638</v>
       </c>
       <c r="B52">
@@ -4534,7 +4536,7 @@
       <c r="G52">
         <v>148.56326772984039</v>
       </c>
-      <c r="H52" s="3">
+      <c r="H52">
         <v>152.35944846589911</v>
       </c>
       <c r="I52">
@@ -4579,7 +4581,7 @@
       <c r="V52">
         <v>52696047</v>
       </c>
-      <c r="W52" s="5">
+      <c r="W52" s="4">
         <v>25.9</v>
       </c>
       <c r="X52">
@@ -4589,8 +4591,8 @@
         <v>1281.45</v>
       </c>
     </row>
-    <row r="53" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A53" s="4">
+    <row r="53" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A53" s="3">
         <v>45639</v>
       </c>
       <c r="B53">
@@ -4611,7 +4613,7 @@
       <c r="G53">
         <v>148.56326772984039</v>
       </c>
-      <c r="H53" s="3">
+      <c r="H53">
         <v>152.35944846589911</v>
       </c>
       <c r="I53">
@@ -4656,7 +4658,7 @@
       <c r="V53">
         <v>52655124</v>
       </c>
-      <c r="W53" s="5">
+      <c r="W53" s="4">
         <v>25.9</v>
       </c>
       <c r="X53">
@@ -4666,8 +4668,8 @@
         <v>1282.5899999999999</v>
       </c>
     </row>
-    <row r="54" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A54" s="4">
+    <row r="54" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A54" s="3">
         <v>45642</v>
       </c>
       <c r="B54">
@@ -4688,7 +4690,7 @@
       <c r="G54">
         <v>148.56326772984039</v>
       </c>
-      <c r="H54" s="3">
+      <c r="H54">
         <v>152.35944846589911</v>
       </c>
       <c r="I54">
@@ -4733,7 +4735,7 @@
       <c r="V54">
         <v>52003911</v>
       </c>
-      <c r="W54" s="5">
+      <c r="W54" s="4">
         <v>25.9</v>
       </c>
       <c r="X54">
@@ -4743,8 +4745,8 @@
         <v>1283.73</v>
       </c>
     </row>
-    <row r="55" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A55" s="4">
+    <row r="55" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A55" s="3">
         <v>45643</v>
       </c>
       <c r="B55">
@@ -4765,7 +4767,7 @@
       <c r="G55">
         <v>148.56326772984039</v>
       </c>
-      <c r="H55" s="3">
+      <c r="H55">
         <v>152.35944846589911</v>
       </c>
       <c r="I55">
@@ -4810,7 +4812,7 @@
       <c r="V55">
         <v>52505151</v>
       </c>
-      <c r="W55" s="5">
+      <c r="W55" s="4">
         <v>25.9</v>
       </c>
       <c r="X55">
@@ -4820,8 +4822,8 @@
         <v>1286.99</v>
       </c>
     </row>
-    <row r="56" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A56" s="4">
+    <row r="56" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A56" s="3">
         <v>45644</v>
       </c>
       <c r="B56">
@@ -4842,7 +4844,7 @@
       <c r="G56">
         <v>148.56326772984039</v>
       </c>
-      <c r="H56" s="3">
+      <c r="H56">
         <v>152.35944846589911</v>
       </c>
       <c r="I56">
@@ -4887,7 +4889,7 @@
       <c r="V56">
         <v>52533584</v>
       </c>
-      <c r="W56" s="5">
+      <c r="W56" s="4">
         <v>25.9</v>
       </c>
       <c r="X56">
@@ -4897,8 +4899,8 @@
         <v>1287.98</v>
       </c>
     </row>
-    <row r="57" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A57" s="4">
+    <row r="57" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A57" s="3">
         <v>45645</v>
       </c>
       <c r="B57">
@@ -4919,7 +4921,7 @@
       <c r="G57">
         <v>148.56326772984039</v>
       </c>
-      <c r="H57" s="3">
+      <c r="H57">
         <v>152.35944846589911</v>
       </c>
       <c r="I57">
@@ -4964,7 +4966,7 @@
       <c r="V57">
         <v>52429371</v>
       </c>
-      <c r="W57" s="5">
+      <c r="W57" s="4">
         <v>25.9</v>
       </c>
       <c r="X57">
@@ -4974,8 +4976,8 @@
         <v>1288.96</v>
       </c>
     </row>
-    <row r="58" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A58" s="4">
+    <row r="58" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A58" s="3">
         <v>45646</v>
       </c>
       <c r="B58">
@@ -4996,7 +4998,7 @@
       <c r="G58">
         <v>148.56326772984039</v>
       </c>
-      <c r="H58" s="3">
+      <c r="H58">
         <v>152.35944846589911</v>
       </c>
       <c r="I58">
@@ -5041,7 +5043,7 @@
       <c r="V58">
         <v>52365161</v>
       </c>
-      <c r="W58" s="5">
+      <c r="W58" s="4">
         <v>25.9</v>
       </c>
       <c r="X58">
@@ -5051,8 +5053,8 @@
         <v>1289.95</v>
       </c>
     </row>
-    <row r="59" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A59" s="4">
+    <row r="59" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A59" s="3">
         <v>45649</v>
       </c>
       <c r="B59">
@@ -5073,7 +5075,7 @@
       <c r="G59">
         <v>148.56326772984039</v>
       </c>
-      <c r="H59" s="3">
+      <c r="H59">
         <v>152.35944846589911</v>
       </c>
       <c r="I59">
@@ -5118,7 +5120,7 @@
       <c r="V59">
         <v>51912898</v>
       </c>
-      <c r="W59" s="5">
+      <c r="W59" s="4">
         <v>25.9</v>
       </c>
       <c r="X59">
@@ -5128,8 +5130,8 @@
         <v>1290.94</v>
       </c>
     </row>
-    <row r="60" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A60" s="4">
+    <row r="60" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A60" s="3">
         <v>45650</v>
       </c>
       <c r="B60">
@@ -5150,13 +5152,13 @@
       <c r="G60">
         <v>148.56326772984039</v>
       </c>
-      <c r="H60" s="3">
+      <c r="H60">
         <v>152.35944846589911</v>
       </c>
       <c r="I60">
         <v>149.96193649350377</v>
       </c>
-      <c r="W60" s="5">
+      <c r="W60" s="4">
         <v>25.9</v>
       </c>
       <c r="X60">
@@ -5166,8 +5168,8 @@
         <v>1293.9000000000001</v>
       </c>
     </row>
-    <row r="61" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A61" s="4">
+    <row r="61" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A61" s="3">
         <v>45652</v>
       </c>
       <c r="B61">
@@ -5188,7 +5190,7 @@
       <c r="G61">
         <v>148.56326772984039</v>
       </c>
-      <c r="H61" s="3">
+      <c r="H61">
         <v>152.35944846589911</v>
       </c>
       <c r="I61">
@@ -5233,7 +5235,7 @@
       <c r="V61">
         <v>52126096</v>
       </c>
-      <c r="W61" s="5">
+      <c r="W61" s="4">
         <v>25.9</v>
       </c>
       <c r="X61">
@@ -5243,8 +5245,8 @@
         <v>1294.8900000000001</v>
       </c>
     </row>
-    <row r="62" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A62" s="4">
+    <row r="62" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A62" s="3">
         <v>45653</v>
       </c>
       <c r="B62">
@@ -5265,7 +5267,7 @@
       <c r="G62">
         <v>148.56326772984039</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62">
         <v>152.35944846589911</v>
       </c>
       <c r="I62">
@@ -5310,7 +5312,7 @@
       <c r="V62">
         <v>52198917</v>
       </c>
-      <c r="W62" s="5">
+      <c r="W62" s="4">
         <v>25.9</v>
       </c>
       <c r="X62">
@@ -5320,8 +5322,8 @@
         <v>1296.8800000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A63" s="4">
+    <row r="63" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A63" s="3">
         <v>45656</v>
       </c>
       <c r="B63">
@@ -5342,7 +5344,7 @@
       <c r="G63">
         <v>148.56326772984039</v>
       </c>
-      <c r="H63" s="3">
+      <c r="H63">
         <v>152.35944846589911</v>
       </c>
       <c r="I63">
@@ -5387,7 +5389,7 @@
       <c r="V63">
         <v>48662128</v>
       </c>
-      <c r="W63" s="5">
+      <c r="W63" s="4">
         <v>25.9</v>
       </c>
       <c r="X63">
@@ -5397,8 +5399,8 @@
         <v>1297.8699999999999</v>
       </c>
     </row>
-    <row r="64" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A64" s="4">
+    <row r="64" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A64" s="3">
         <v>45659</v>
       </c>
       <c r="B64">
@@ -5419,7 +5421,7 @@
       <c r="G64">
         <v>146.26867372149835</v>
       </c>
-      <c r="H64" s="3">
+      <c r="H64">
         <v>152.2755232300197</v>
       </c>
       <c r="I64">
@@ -5464,7 +5466,7 @@
       <c r="V64">
         <v>49287221</v>
       </c>
-      <c r="W64" s="5">
+      <c r="W64" s="4">
         <v>21.9</v>
       </c>
       <c r="X64">
@@ -5474,8 +5476,8 @@
         <v>1301.8499999999999</v>
       </c>
     </row>
-    <row r="65" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A65" s="4">
+    <row r="65" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A65" s="3">
         <v>45660</v>
       </c>
       <c r="B65">
@@ -5496,7 +5498,7 @@
       <c r="G65">
         <v>146.26867372149835</v>
       </c>
-      <c r="H65" s="3">
+      <c r="H65">
         <v>152.2755232300197</v>
       </c>
       <c r="I65">
@@ -5541,7 +5543,7 @@
       <c r="V65">
         <v>53699883</v>
       </c>
-      <c r="W65" s="5">
+      <c r="W65" s="4">
         <v>21.9</v>
       </c>
       <c r="X65">
@@ -5551,8 +5553,8 @@
         <v>1303.8399999999999</v>
       </c>
     </row>
-    <row r="66" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A66" s="4">
+    <row r="66" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A66" s="3">
         <v>45663</v>
       </c>
       <c r="B66">
@@ -5573,7 +5575,7 @@
       <c r="G66">
         <v>146.26867372149835</v>
       </c>
-      <c r="H66" s="3">
+      <c r="H66">
         <v>152.2755232300197</v>
       </c>
       <c r="I66">
@@ -5618,7 +5620,7 @@
       <c r="V66">
         <v>53200265</v>
       </c>
-      <c r="W66" s="5">
+      <c r="W66" s="4">
         <v>21.9</v>
       </c>
       <c r="X66">
@@ -5628,8 +5630,8 @@
         <v>1304.8399999999999</v>
       </c>
     </row>
-    <row r="67" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A67" s="4">
+    <row r="67" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A67" s="3">
         <v>45664</v>
       </c>
       <c r="B67">
@@ -5650,7 +5652,7 @@
       <c r="G67">
         <v>146.26867372149835</v>
       </c>
-      <c r="H67" s="3">
+      <c r="H67">
         <v>152.2755232300197</v>
       </c>
       <c r="I67">
@@ -5695,7 +5697,7 @@
       <c r="V67">
         <v>53630093</v>
       </c>
-      <c r="W67" s="5">
+      <c r="W67" s="4">
         <v>21.9</v>
       </c>
       <c r="X67">
@@ -5705,8 +5707,8 @@
         <v>1307.8399999999999</v>
       </c>
     </row>
-    <row r="68" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A68" s="4">
+    <row r="68" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A68" s="3">
         <v>45665</v>
       </c>
       <c r="B68">
@@ -5727,7 +5729,7 @@
       <c r="G68">
         <v>146.26867372149835</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68">
         <v>152.2755232300197</v>
       </c>
       <c r="I68">
@@ -5772,7 +5774,7 @@
       <c r="V68">
         <v>53610605</v>
       </c>
-      <c r="W68" s="5">
+      <c r="W68" s="4">
         <v>21.9</v>
       </c>
       <c r="X68">
@@ -5782,8 +5784,8 @@
         <v>1308.8399999999999</v>
       </c>
     </row>
-    <row r="69" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A69" s="4">
+    <row r="69" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A69" s="3">
         <v>45666</v>
       </c>
       <c r="B69">
@@ -5804,7 +5806,7 @@
       <c r="G69">
         <v>146.26867372149835</v>
       </c>
-      <c r="H69" s="3">
+      <c r="H69">
         <v>152.2755232300197</v>
       </c>
       <c r="I69">
@@ -5849,7 +5851,7 @@
       <c r="V69">
         <v>53852259</v>
       </c>
-      <c r="W69" s="5">
+      <c r="W69" s="4">
         <v>21.9</v>
       </c>
       <c r="X69">
@@ -5859,8 +5861,8 @@
         <v>1309.8399999999999</v>
       </c>
     </row>
-    <row r="70" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A70" s="4">
+    <row r="70" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A70" s="3">
         <v>45667</v>
       </c>
       <c r="B70">
@@ -5881,7 +5883,7 @@
       <c r="G70">
         <v>146.26867372149835</v>
       </c>
-      <c r="H70" s="3">
+      <c r="H70">
         <v>152.2755232300197</v>
       </c>
       <c r="I70">
@@ -5926,7 +5928,7 @@
       <c r="V70">
         <v>54118823</v>
       </c>
-      <c r="W70" s="5">
+      <c r="W70" s="4">
         <v>21.9</v>
       </c>
       <c r="X70">
@@ -5936,8 +5938,8 @@
         <v>1310.84</v>
       </c>
     </row>
-    <row r="71" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A71" s="4">
+    <row r="71" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A71" s="3">
         <v>45670</v>
       </c>
       <c r="B71">
@@ -5958,7 +5960,7 @@
       <c r="G71">
         <v>146.26867372149835</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71">
         <v>152.2755232300197</v>
       </c>
       <c r="I71">
@@ -6003,7 +6005,7 @@
       <c r="V71">
         <v>53900096</v>
       </c>
-      <c r="W71" s="5">
+      <c r="W71" s="4">
         <v>21.9</v>
       </c>
       <c r="X71">
@@ -6013,8 +6015,8 @@
         <v>1311.85</v>
       </c>
     </row>
-    <row r="72" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A72" s="4">
+    <row r="72" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A72" s="3">
         <v>45671</v>
       </c>
       <c r="B72">
@@ -6035,7 +6037,7 @@
       <c r="G72">
         <v>146.26867372149835</v>
       </c>
-      <c r="H72" s="3">
+      <c r="H72">
         <v>152.2755232300197</v>
       </c>
       <c r="I72">
@@ -6080,7 +6082,7 @@
       <c r="V72">
         <v>55143348</v>
       </c>
-      <c r="W72" s="5">
+      <c r="W72" s="4">
         <v>21.9</v>
       </c>
       <c r="X72">
@@ -6090,8 +6092,8 @@
         <v>1314.86</v>
       </c>
     </row>
-    <row r="73" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A73" s="4">
+    <row r="73" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A73" s="3">
         <v>45672</v>
       </c>
       <c r="B73">
@@ -6112,7 +6114,7 @@
       <c r="G73">
         <v>146.26867372149835</v>
       </c>
-      <c r="H73" s="3">
+      <c r="H73">
         <v>152.2755232300197</v>
       </c>
       <c r="I73">
@@ -6157,7 +6159,7 @@
       <c r="V73">
         <v>55665059</v>
       </c>
-      <c r="W73" s="5">
+      <c r="W73" s="4">
         <v>21.9</v>
       </c>
       <c r="X73">
@@ -6167,8 +6169,8 @@
         <v>1315.87</v>
       </c>
     </row>
-    <row r="74" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A74" s="4">
+    <row r="74" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A74" s="3">
         <v>45673</v>
       </c>
       <c r="B74">
@@ -6189,7 +6191,7 @@
       <c r="G74">
         <v>146.26867372149835</v>
       </c>
-      <c r="H74" s="3">
+      <c r="H74">
         <v>152.2755232300197</v>
       </c>
       <c r="I74">
@@ -6234,7 +6236,7 @@
       <c r="V74">
         <v>56370519</v>
       </c>
-      <c r="W74" s="5">
+      <c r="W74" s="4">
         <v>21.9</v>
       </c>
       <c r="X74">
@@ -6244,8 +6246,8 @@
         <v>1316.87</v>
       </c>
     </row>
-    <row r="75" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A75" s="4">
+    <row r="75" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A75" s="3">
         <v>45674</v>
       </c>
       <c r="B75">
@@ -6266,7 +6268,7 @@
       <c r="G75">
         <v>146.26867372149835</v>
       </c>
-      <c r="H75" s="3">
+      <c r="H75">
         <v>152.2755232300197</v>
       </c>
       <c r="I75">
@@ -6311,7 +6313,7 @@
       <c r="V75">
         <v>56400344</v>
       </c>
-      <c r="W75" s="5">
+      <c r="W75" s="4">
         <v>21.9</v>
       </c>
       <c r="X75">
@@ -6321,8 +6323,8 @@
         <v>1318.01</v>
       </c>
     </row>
-    <row r="76" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A76" s="4">
+    <row r="76" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A76" s="3">
         <v>45677</v>
       </c>
       <c r="B76">
@@ -6334,7 +6336,7 @@
       <c r="G76">
         <v>146.26867372149835</v>
       </c>
-      <c r="H76" s="3">
+      <c r="H76">
         <v>152.2755232300197</v>
       </c>
       <c r="I76">
@@ -6379,7 +6381,7 @@
       <c r="V76">
         <v>55908359</v>
       </c>
-      <c r="W76" s="5">
+      <c r="W76" s="4">
         <v>21.9</v>
       </c>
       <c r="X76">
@@ -6389,8 +6391,8 @@
         <v>1319.14</v>
       </c>
     </row>
-    <row r="77" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A77" s="4">
+    <row r="77" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A77" s="3">
         <v>45678</v>
       </c>
       <c r="B77">
@@ -6411,7 +6413,7 @@
       <c r="G77">
         <v>146.26867372149835</v>
       </c>
-      <c r="H77" s="3">
+      <c r="H77">
         <v>152.2755232300197</v>
       </c>
       <c r="I77">
@@ -6456,7 +6458,7 @@
       <c r="V77">
         <v>56685637</v>
       </c>
-      <c r="W77" s="5">
+      <c r="W77" s="4">
         <v>21.9</v>
       </c>
       <c r="X77">
@@ -6466,8 +6468,8 @@
         <v>1322.54</v>
       </c>
     </row>
-    <row r="78" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A78" s="4">
+    <row r="78" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A78" s="3">
         <v>45679</v>
       </c>
       <c r="B78">
@@ -6488,7 +6490,7 @@
       <c r="G78">
         <v>146.26867372149835</v>
       </c>
-      <c r="H78" s="3">
+      <c r="H78">
         <v>152.2755232300197</v>
       </c>
       <c r="I78">
@@ -6533,7 +6535,7 @@
       <c r="V78">
         <v>57058625</v>
       </c>
-      <c r="W78" s="5">
+      <c r="W78" s="4">
         <v>21.9</v>
       </c>
       <c r="X78">
@@ -6543,8 +6545,8 @@
         <v>1323.68</v>
       </c>
     </row>
-    <row r="79" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A79" s="4">
+    <row r="79" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A79" s="3">
         <v>45680</v>
       </c>
       <c r="B79">
@@ -6565,7 +6567,7 @@
       <c r="G79">
         <v>146.26867372149835</v>
       </c>
-      <c r="H79" s="3">
+      <c r="H79">
         <v>152.2755232300197</v>
       </c>
       <c r="I79">
@@ -6610,7 +6612,7 @@
       <c r="V79">
         <v>57146554</v>
       </c>
-      <c r="W79" s="5">
+      <c r="W79" s="4">
         <v>21.9</v>
       </c>
       <c r="X79">
@@ -6620,8 +6622,8 @@
         <v>1324.82</v>
       </c>
     </row>
-    <row r="80" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A80" s="4">
+    <row r="80" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A80" s="3">
         <v>45681</v>
       </c>
       <c r="B80">
@@ -6642,7 +6644,7 @@
       <c r="G80">
         <v>146.26867372149835</v>
       </c>
-      <c r="H80" s="3">
+      <c r="H80">
         <v>152.2755232300197</v>
       </c>
       <c r="I80">
@@ -6687,7 +6689,7 @@
       <c r="V80">
         <v>57923582</v>
       </c>
-      <c r="W80" s="5">
+      <c r="W80" s="4">
         <v>21.9</v>
       </c>
       <c r="X80">
@@ -6697,8 +6699,8 @@
         <v>1325.96</v>
       </c>
     </row>
-    <row r="81" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A81" s="4">
+    <row r="81" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A81" s="3">
         <v>45684</v>
       </c>
       <c r="B81">
@@ -6719,7 +6721,7 @@
       <c r="G81">
         <v>146.26867372149835</v>
       </c>
-      <c r="H81" s="3">
+      <c r="H81">
         <v>152.2755232300197</v>
       </c>
       <c r="I81">
@@ -6764,7 +6766,7 @@
       <c r="V81">
         <v>56787311</v>
       </c>
-      <c r="W81" s="5">
+      <c r="W81" s="4">
         <v>21.9</v>
       </c>
       <c r="X81">
@@ -6774,8 +6776,8 @@
         <v>1327.1</v>
       </c>
     </row>
-    <row r="82" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A82" s="4">
+    <row r="82" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A82" s="3">
         <v>45685</v>
       </c>
       <c r="B82">
@@ -6796,7 +6798,7 @@
       <c r="G82">
         <v>146.26867372149835</v>
       </c>
-      <c r="H82" s="3">
+      <c r="H82">
         <v>152.2755232300197</v>
       </c>
       <c r="I82">
@@ -6841,7 +6843,7 @@
       <c r="V82">
         <v>57357861</v>
       </c>
-      <c r="W82" s="5">
+      <c r="W82" s="4">
         <v>21.9</v>
       </c>
       <c r="X82">
@@ -6851,8 +6853,8 @@
         <v>1330.52</v>
       </c>
     </row>
-    <row r="83" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A83" s="4">
+    <row r="83" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A83" s="3">
         <v>45686</v>
       </c>
       <c r="B83">
@@ -6873,7 +6875,7 @@
       <c r="G83">
         <v>146.26867372149835</v>
       </c>
-      <c r="H83" s="3">
+      <c r="H83">
         <v>152.2755232300197</v>
       </c>
       <c r="I83">
@@ -6918,7 +6920,7 @@
       <c r="V83">
         <v>56597143</v>
       </c>
-      <c r="W83" s="5">
+      <c r="W83" s="4">
         <v>21.9</v>
       </c>
       <c r="X83">
@@ -6928,8 +6930,8 @@
         <v>1331.67</v>
       </c>
     </row>
-    <row r="84" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A84" s="4">
+    <row r="84" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A84" s="3">
         <v>45687</v>
       </c>
       <c r="B84">
@@ -6950,7 +6952,7 @@
       <c r="G84">
         <v>146.26867372149835</v>
       </c>
-      <c r="H84" s="3">
+      <c r="H84">
         <v>152.2755232300197</v>
       </c>
       <c r="I84">
@@ -6995,7 +6997,7 @@
       <c r="V84">
         <v>56605875</v>
       </c>
-      <c r="W84" s="5">
+      <c r="W84" s="4">
         <v>21.9</v>
       </c>
       <c r="X84">
@@ -7005,8 +7007,8 @@
         <v>1332.81</v>
       </c>
     </row>
-    <row r="85" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A85" s="4">
+    <row r="85" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A85" s="3">
         <v>45688</v>
       </c>
       <c r="B85">
@@ -7027,7 +7029,7 @@
       <c r="G85">
         <v>146.26867372149835</v>
       </c>
-      <c r="H85" s="3">
+      <c r="H85">
         <v>152.2755232300197</v>
       </c>
       <c r="I85">
@@ -7072,7 +7074,7 @@
       <c r="V85">
         <v>56575423</v>
       </c>
-      <c r="W85" s="5">
+      <c r="W85" s="4">
         <v>21.9</v>
       </c>
       <c r="X85">
@@ -7082,8 +7084,8 @@
         <v>1333.96</v>
       </c>
     </row>
-    <row r="86" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A86" s="4">
+    <row r="86" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A86" s="3">
         <v>45691</v>
       </c>
       <c r="B86">
@@ -7104,7 +7106,7 @@
       <c r="G86">
         <v>141.16009340187153</v>
       </c>
-      <c r="H86" s="3">
+      <c r="H86">
         <v>153.37898361956226</v>
       </c>
       <c r="I86">
@@ -7149,7 +7151,7 @@
       <c r="V86">
         <v>56318030</v>
       </c>
-      <c r="W86" s="5">
+      <c r="W86" s="4">
         <v>22.2</v>
       </c>
       <c r="X86">
@@ -7159,8 +7161,8 @@
         <v>1335.11</v>
       </c>
     </row>
-    <row r="87" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A87" s="4">
+    <row r="87" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A87" s="3">
         <v>45692</v>
       </c>
       <c r="B87">
@@ -7181,7 +7183,7 @@
       <c r="G87">
         <v>141.16009340187153</v>
       </c>
-      <c r="H87" s="3">
+      <c r="H87">
         <v>153.37898361956226</v>
       </c>
       <c r="I87">
@@ -7226,7 +7228,7 @@
       <c r="V87">
         <v>57537462</v>
       </c>
-      <c r="W87" s="5">
+      <c r="W87" s="4">
         <v>22.2</v>
       </c>
       <c r="X87">
@@ -7236,8 +7238,8 @@
         <v>1338.55</v>
       </c>
     </row>
-    <row r="88" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A88" s="4">
+    <row r="88" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A88" s="3">
         <v>45693</v>
       </c>
       <c r="B88">
@@ -7258,7 +7260,7 @@
       <c r="G88">
         <v>141.16009340187153</v>
       </c>
-      <c r="H88" s="3">
+      <c r="H88">
         <v>153.37898361956226</v>
       </c>
       <c r="I88">
@@ -7303,7 +7305,7 @@
       <c r="V88">
         <v>57912763</v>
       </c>
-      <c r="W88" s="5">
+      <c r="W88" s="4">
         <v>22.2</v>
       </c>
       <c r="X88">
@@ -7313,8 +7315,8 @@
         <v>1339.7</v>
       </c>
     </row>
-    <row r="89" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A89" s="4">
+    <row r="89" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A89" s="3">
         <v>45694</v>
       </c>
       <c r="B89">
@@ -7335,7 +7337,7 @@
       <c r="G89">
         <v>141.16009340187153</v>
       </c>
-      <c r="H89" s="3">
+      <c r="H89">
         <v>153.37898361956226</v>
       </c>
       <c r="I89">
@@ -7380,7 +7382,7 @@
       <c r="V89">
         <v>58397945</v>
       </c>
-      <c r="W89" s="5">
+      <c r="W89" s="4">
         <v>22.2</v>
       </c>
       <c r="X89">
@@ -7390,8 +7392,8 @@
         <v>1340.86</v>
       </c>
     </row>
-    <row r="90" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A90" s="4">
+    <row r="90" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A90" s="3">
         <v>45695</v>
       </c>
       <c r="B90">
@@ -7412,7 +7414,7 @@
       <c r="G90">
         <v>141.16009340187153</v>
       </c>
-      <c r="H90" s="3">
+      <c r="H90">
         <v>153.37898361956226</v>
       </c>
       <c r="I90">
@@ -7457,7 +7459,7 @@
       <c r="V90">
         <v>59258417</v>
       </c>
-      <c r="W90" s="5">
+      <c r="W90" s="4">
         <v>22.2</v>
       </c>
       <c r="X90">
@@ -7467,8 +7469,8 @@
         <v>1342.01</v>
       </c>
     </row>
-    <row r="91" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A91" s="4">
+    <row r="91" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A91" s="3">
         <v>45698</v>
       </c>
       <c r="B91">
@@ -7489,7 +7491,7 @@
       <c r="G91">
         <v>141.16009340187153</v>
       </c>
-      <c r="H91" s="3">
+      <c r="H91">
         <v>153.37898361956226</v>
       </c>
       <c r="I91">
@@ -7534,7 +7536,7 @@
       <c r="V91">
         <v>58713817</v>
       </c>
-      <c r="W91" s="5">
+      <c r="W91" s="4">
         <v>22.2</v>
       </c>
       <c r="X91">
@@ -7544,8 +7546,8 @@
         <v>1343.16</v>
       </c>
     </row>
-    <row r="92" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A92" s="4">
+    <row r="92" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A92" s="3">
         <v>45699</v>
       </c>
       <c r="B92">
@@ -7566,7 +7568,7 @@
       <c r="G92">
         <v>141.16009340187153</v>
       </c>
-      <c r="H92" s="3">
+      <c r="H92">
         <v>153.37898361956226</v>
       </c>
       <c r="I92">
@@ -7611,7 +7613,7 @@
       <c r="V92">
         <v>58965978</v>
       </c>
-      <c r="W92" s="5">
+      <c r="W92" s="4">
         <v>22.2</v>
       </c>
       <c r="X92">
@@ -7621,8 +7623,8 @@
         <v>1346.63</v>
       </c>
     </row>
-    <row r="93" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A93" s="4">
+    <row r="93" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A93" s="3">
         <v>45700</v>
       </c>
       <c r="B93">
@@ -7643,7 +7645,7 @@
       <c r="G93">
         <v>141.16009340187153</v>
       </c>
-      <c r="H93" s="3">
+      <c r="H93">
         <v>153.37898361956226</v>
       </c>
       <c r="I93">
@@ -7688,7 +7690,7 @@
       <c r="V93">
         <v>58967311</v>
       </c>
-      <c r="W93" s="5">
+      <c r="W93" s="4">
         <v>22.2</v>
       </c>
       <c r="X93">
@@ -7698,8 +7700,8 @@
         <v>1347.79</v>
       </c>
     </row>
-    <row r="94" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A94" s="4">
+    <row r="94" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A94" s="3">
         <v>45701</v>
       </c>
       <c r="B94">
@@ -7720,7 +7722,7 @@
       <c r="G94">
         <v>141.16009340187153</v>
       </c>
-      <c r="H94" s="3">
+      <c r="H94">
         <v>153.37898361956226</v>
       </c>
       <c r="I94">
@@ -7765,7 +7767,7 @@
       <c r="V94">
         <v>59913169</v>
       </c>
-      <c r="W94" s="5">
+      <c r="W94" s="4">
         <v>22.2</v>
       </c>
       <c r="X94">
@@ -7775,8 +7777,8 @@
         <v>1348.95</v>
       </c>
     </row>
-    <row r="95" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A95" s="4">
+    <row r="95" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A95" s="3">
         <v>45702</v>
       </c>
       <c r="B95">
@@ -7797,7 +7799,7 @@
       <c r="G95">
         <v>141.16009340187153</v>
       </c>
-      <c r="H95" s="3">
+      <c r="H95">
         <v>153.37898361956226</v>
       </c>
       <c r="I95">
@@ -7842,7 +7844,7 @@
       <c r="V95">
         <v>60929173</v>
       </c>
-      <c r="W95" s="5">
+      <c r="W95" s="4">
         <v>22.2</v>
       </c>
       <c r="X95">
@@ -7852,8 +7854,8 @@
         <v>1350.11</v>
       </c>
     </row>
-    <row r="96" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A96" s="4">
+    <row r="96" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A96" s="3">
         <v>45705</v>
       </c>
       <c r="B96">
@@ -7865,7 +7867,7 @@
       <c r="G96">
         <v>141.16009340187153</v>
       </c>
-      <c r="H96" s="3">
+      <c r="H96">
         <v>153.37898361956226</v>
       </c>
       <c r="I96">
@@ -7910,7 +7912,7 @@
       <c r="V96">
         <v>60804909</v>
       </c>
-      <c r="W96" s="5">
+      <c r="W96" s="4">
         <v>22.2</v>
       </c>
       <c r="X96">
@@ -7920,8 +7922,8 @@
         <v>1351.27</v>
       </c>
     </row>
-    <row r="97" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A97" s="4">
+    <row r="97" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A97" s="3">
         <v>45706</v>
       </c>
       <c r="B97">
@@ -7942,7 +7944,7 @@
       <c r="G97">
         <v>141.16009340187153</v>
       </c>
-      <c r="H97" s="3">
+      <c r="H97">
         <v>153.37898361956226</v>
       </c>
       <c r="I97">
@@ -7987,7 +7989,7 @@
       <c r="V97">
         <v>61355264</v>
       </c>
-      <c r="W97" s="5">
+      <c r="W97" s="4">
         <v>22.2</v>
       </c>
       <c r="X97">
@@ -7997,8 +7999,8 @@
         <v>1354.53</v>
       </c>
     </row>
-    <row r="98" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A98" s="4">
+    <row r="98" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A98" s="3">
         <v>45707</v>
       </c>
       <c r="B98">
@@ -8019,7 +8021,7 @@
       <c r="G98">
         <v>141.16009340187153</v>
       </c>
-      <c r="H98" s="3">
+      <c r="H98">
         <v>153.37898361956226</v>
       </c>
       <c r="I98">
@@ -8064,7 +8066,7 @@
       <c r="V98">
         <v>61365407</v>
       </c>
-      <c r="W98" s="5">
+      <c r="W98" s="4">
         <v>22.2</v>
       </c>
       <c r="X98">
@@ -8074,8 +8076,8 @@
         <v>1355.59</v>
       </c>
     </row>
-    <row r="99" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A99" s="4">
+    <row r="99" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A99" s="3">
         <v>45708</v>
       </c>
       <c r="B99">
@@ -8096,7 +8098,7 @@
       <c r="G99">
         <v>141.16009340187153</v>
       </c>
-      <c r="H99" s="3">
+      <c r="H99">
         <v>153.37898361956226</v>
       </c>
       <c r="I99">
@@ -8141,7 +8143,7 @@
       <c r="V99">
         <v>61802619</v>
       </c>
-      <c r="W99" s="5">
+      <c r="W99" s="4">
         <v>22.2</v>
       </c>
       <c r="X99">
@@ -8151,8 +8153,8 @@
         <v>1356.64</v>
       </c>
     </row>
-    <row r="100" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A100" s="4">
+    <row r="100" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A100" s="3">
         <v>45709</v>
       </c>
       <c r="B100">
@@ -8173,7 +8175,7 @@
       <c r="G100">
         <v>141.16009340187153</v>
       </c>
-      <c r="H100" s="3">
+      <c r="H100">
         <v>153.37898361956226</v>
       </c>
       <c r="I100">
@@ -8218,7 +8220,7 @@
       <c r="V100">
         <v>62500425</v>
       </c>
-      <c r="W100" s="5">
+      <c r="W100" s="4">
         <v>22.2</v>
       </c>
       <c r="X100">
@@ -8228,8 +8230,8 @@
         <v>1357.69</v>
       </c>
     </row>
-    <row r="101" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A101" s="4">
+    <row r="101" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A101" s="3">
         <v>45712</v>
       </c>
       <c r="B101">
@@ -8250,7 +8252,7 @@
       <c r="G101">
         <v>141.16009340187153</v>
       </c>
-      <c r="H101" s="3">
+      <c r="H101">
         <v>153.37898361956226</v>
       </c>
       <c r="I101">
@@ -8295,7 +8297,7 @@
       <c r="V101">
         <v>62062333</v>
       </c>
-      <c r="W101" s="5">
+      <c r="W101" s="4">
         <v>22.2</v>
       </c>
       <c r="X101">
@@ -8305,8 +8307,8 @@
         <v>1358.75</v>
       </c>
     </row>
-    <row r="102" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A102" s="4">
+    <row r="102" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A102" s="3">
         <v>45713</v>
       </c>
       <c r="B102">
@@ -8327,7 +8329,7 @@
       <c r="G102">
         <v>141.16009340187153</v>
       </c>
-      <c r="H102" s="3">
+      <c r="H102">
         <v>153.37898361956226</v>
       </c>
       <c r="I102">
@@ -8372,7 +8374,7 @@
       <c r="V102">
         <v>62554465</v>
       </c>
-      <c r="W102" s="5">
+      <c r="W102" s="4">
         <v>22.2</v>
       </c>
       <c r="X102">
@@ -8382,8 +8384,8 @@
         <v>1361.92</v>
       </c>
     </row>
-    <row r="103" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A103" s="4">
+    <row r="103" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A103" s="3">
         <v>45714</v>
       </c>
       <c r="B103">
@@ -8404,7 +8406,7 @@
       <c r="G103">
         <v>141.16009340187153</v>
       </c>
-      <c r="H103" s="3">
+      <c r="H103">
         <v>153.37898361956226</v>
       </c>
       <c r="I103">
@@ -8449,7 +8451,7 @@
       <c r="V103">
         <v>61937022</v>
       </c>
-      <c r="W103" s="5">
+      <c r="W103" s="4">
         <v>22.2</v>
       </c>
       <c r="X103">
@@ -8459,8 +8461,8 @@
         <v>1362.98</v>
       </c>
     </row>
-    <row r="104" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A104" s="4">
+    <row r="104" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A104" s="3">
         <v>45715</v>
       </c>
       <c r="B104">
@@ -8481,7 +8483,7 @@
       <c r="G104">
         <v>141.16009340187153</v>
       </c>
-      <c r="H104" s="3">
+      <c r="H104">
         <v>153.37898361956226</v>
       </c>
       <c r="I104">
@@ -8526,7 +8528,7 @@
       <c r="V104">
         <v>60776858</v>
       </c>
-      <c r="W104" s="5">
+      <c r="W104" s="4">
         <v>22.2</v>
       </c>
       <c r="X104">
@@ -8536,8 +8538,8 @@
         <v>1364.04</v>
       </c>
     </row>
-    <row r="105" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A105" s="4">
+    <row r="105" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A105" s="3">
         <v>45716</v>
       </c>
       <c r="B105">
@@ -8558,7 +8560,7 @@
       <c r="G105">
         <v>141.16009340187153</v>
       </c>
-      <c r="H105" s="3">
+      <c r="H105">
         <v>153.37898361956226</v>
       </c>
       <c r="I105">
@@ -8603,7 +8605,7 @@
       <c r="V105">
         <v>60830785</v>
       </c>
-      <c r="W105" s="5">
+      <c r="W105" s="4">
         <v>22.2</v>
       </c>
       <c r="X105">
@@ -8613,8 +8615,8 @@
         <v>1365.1</v>
       </c>
     </row>
-    <row r="106" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A106" s="4">
+    <row r="106" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A106" s="3">
         <v>45721</v>
       </c>
       <c r="B106">
@@ -8635,7 +8637,7 @@
       <c r="G106">
         <v>150.38089244694868</v>
       </c>
-      <c r="H106" s="3">
+      <c r="H106">
         <v>150.57566380116401</v>
       </c>
       <c r="I106">
@@ -8680,7 +8682,7 @@
       <c r="V106">
         <v>59498832</v>
       </c>
-      <c r="W106" s="5">
+      <c r="W106" s="4">
         <v>24.5</v>
       </c>
       <c r="X106">
@@ -8690,8 +8692,8 @@
         <v>1366.16</v>
       </c>
     </row>
-    <row r="107" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A107" s="4">
+    <row r="107" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A107" s="3">
         <v>45722</v>
       </c>
       <c r="B107">
@@ -8712,7 +8714,7 @@
       <c r="G107">
         <v>150.38089244694868</v>
       </c>
-      <c r="H107" s="3">
+      <c r="H107">
         <v>150.57566380116401</v>
       </c>
       <c r="I107">
@@ -8757,7 +8759,7 @@
       <c r="V107">
         <v>59464769</v>
       </c>
-      <c r="W107" s="5">
+      <c r="W107" s="4">
         <v>24.5</v>
       </c>
       <c r="X107">
@@ -8767,8 +8769,8 @@
         <v>1371.48</v>
       </c>
     </row>
-    <row r="108" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A108" s="4">
+    <row r="108" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A108" s="3">
         <v>45723</v>
       </c>
       <c r="B108">
@@ -8789,7 +8791,7 @@
       <c r="G108">
         <v>150.38089244694868</v>
       </c>
-      <c r="H108" s="3">
+      <c r="H108">
         <v>150.57566380116401</v>
       </c>
       <c r="I108">
@@ -8834,7 +8836,7 @@
       <c r="V108">
         <v>60055603</v>
       </c>
-      <c r="W108" s="5">
+      <c r="W108" s="4">
         <v>24.5</v>
       </c>
       <c r="X108">
@@ -8844,8 +8846,8 @@
         <v>1372.55</v>
       </c>
     </row>
-    <row r="109" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A109" s="4">
+    <row r="109" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A109" s="3">
         <v>45726</v>
       </c>
       <c r="B109">
@@ -8866,7 +8868,7 @@
       <c r="G109">
         <v>150.38089244694868</v>
       </c>
-      <c r="H109" s="3">
+      <c r="H109">
         <v>150.57566380116401</v>
       </c>
       <c r="I109">
@@ -8911,7 +8913,7 @@
       <c r="V109">
         <v>59020111</v>
       </c>
-      <c r="W109" s="5">
+      <c r="W109" s="4">
         <v>24.5</v>
       </c>
       <c r="X109">
@@ -8921,8 +8923,8 @@
         <v>1373.61</v>
       </c>
     </row>
-    <row r="110" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A110" s="4">
+    <row r="110" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A110" s="3">
         <v>45727</v>
       </c>
       <c r="B110">
@@ -8943,7 +8945,7 @@
       <c r="G110">
         <v>150.38089244694868</v>
       </c>
-      <c r="H110" s="3">
+      <c r="H110">
         <v>150.57566380116401</v>
       </c>
       <c r="I110">
@@ -8988,7 +8990,7 @@
       <c r="V110">
         <v>59270940</v>
       </c>
-      <c r="W110" s="5">
+      <c r="W110" s="4">
         <v>24.5</v>
       </c>
       <c r="X110">
@@ -8998,8 +9000,8 @@
         <v>1376.82</v>
       </c>
     </row>
-    <row r="111" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A111" s="4">
+    <row r="111" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A111" s="3">
         <v>45728</v>
       </c>
       <c r="B111">
@@ -9020,7 +9022,7 @@
       <c r="G111">
         <v>150.38089244694868</v>
       </c>
-      <c r="H111" s="3">
+      <c r="H111">
         <v>150.57566380116401</v>
       </c>
       <c r="I111">
@@ -9065,7 +9067,7 @@
       <c r="V111">
         <v>59109877</v>
       </c>
-      <c r="W111" s="5">
+      <c r="W111" s="4">
         <v>24.5</v>
       </c>
       <c r="X111">
@@ -9075,8 +9077,8 @@
         <v>1377.89</v>
       </c>
     </row>
-    <row r="112" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A112" s="4">
+    <row r="112" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A112" s="3">
         <v>45729</v>
       </c>
       <c r="B112">
@@ -9097,7 +9099,7 @@
       <c r="G112">
         <v>150.38089244694868</v>
       </c>
-      <c r="H112" s="3">
+      <c r="H112">
         <v>150.57566380116401</v>
       </c>
       <c r="I112">
@@ -9142,7 +9144,7 @@
       <c r="V112">
         <v>59367336</v>
       </c>
-      <c r="W112" s="5">
+      <c r="W112" s="4">
         <v>24.5</v>
       </c>
       <c r="X112">
@@ -9152,8 +9154,8 @@
         <v>1378.96</v>
       </c>
     </row>
-    <row r="113" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A113" s="4">
+    <row r="113" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A113" s="3">
         <v>45730</v>
       </c>
       <c r="B113">
@@ -9174,7 +9176,7 @@
       <c r="G113">
         <v>150.38089244694868</v>
       </c>
-      <c r="H113" s="3">
+      <c r="H113">
         <v>150.57566380116401</v>
       </c>
       <c r="I113">
@@ -9219,7 +9221,7 @@
       <c r="V113">
         <v>60081314</v>
       </c>
-      <c r="W113" s="5">
+      <c r="W113" s="4">
         <v>24.5</v>
       </c>
       <c r="X113">
@@ -9229,8 +9231,8 @@
         <v>1380.03</v>
       </c>
     </row>
-    <row r="114" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A114" s="4">
+    <row r="114" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A114" s="3">
         <v>45733</v>
       </c>
       <c r="B114">
@@ -9251,7 +9253,7 @@
       <c r="G114">
         <v>150.38089244694868</v>
       </c>
-      <c r="H114" s="3">
+      <c r="H114">
         <v>150.57566380116401</v>
       </c>
       <c r="I114">
@@ -9296,7 +9298,7 @@
       <c r="V114">
         <v>59762258</v>
       </c>
-      <c r="W114" s="5">
+      <c r="W114" s="4">
         <v>24.5</v>
       </c>
       <c r="X114">
@@ -9306,8 +9308,8 @@
         <v>1381.11</v>
       </c>
     </row>
-    <row r="115" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A115" s="4">
+    <row r="115" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A115" s="3">
         <v>45734</v>
       </c>
       <c r="B115">
@@ -9328,7 +9330,7 @@
       <c r="G115">
         <v>150.38089244694868</v>
       </c>
-      <c r="H115" s="3">
+      <c r="H115">
         <v>150.57566380116401</v>
       </c>
       <c r="I115">
@@ -9373,7 +9375,7 @@
       <c r="V115">
         <v>60436300</v>
       </c>
-      <c r="W115" s="5">
+      <c r="W115" s="4">
         <v>24.5</v>
       </c>
       <c r="X115">
@@ -9383,8 +9385,8 @@
         <v>1384.3</v>
       </c>
     </row>
-    <row r="116" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A116" s="4">
+    <row r="116" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A116" s="3">
         <v>45735</v>
       </c>
       <c r="B116">
@@ -9405,7 +9407,7 @@
       <c r="G116">
         <v>150.38089244694868</v>
       </c>
-      <c r="H116" s="3">
+      <c r="H116">
         <v>150.57566380116401</v>
       </c>
       <c r="I116">
@@ -9450,7 +9452,7 @@
       <c r="V116">
         <v>60673900</v>
       </c>
-      <c r="W116" s="5">
+      <c r="W116" s="4">
         <v>24.5</v>
       </c>
       <c r="X116">
@@ -9460,8 +9462,8 @@
         <v>1385.36</v>
       </c>
     </row>
-    <row r="117" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A117" s="4">
+    <row r="117" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A117" s="3">
         <v>45736</v>
       </c>
       <c r="B117">
@@ -9482,7 +9484,7 @@
       <c r="G117">
         <v>150.38089244694868</v>
       </c>
-      <c r="H117" s="3">
+      <c r="H117">
         <v>150.57566380116401</v>
       </c>
       <c r="I117">
@@ -9527,7 +9529,7 @@
       <c r="V117">
         <v>61180726</v>
       </c>
-      <c r="W117" s="5">
+      <c r="W117" s="4">
         <v>24.5</v>
       </c>
       <c r="X117">
@@ -9537,8 +9539,8 @@
         <v>1386.42</v>
       </c>
     </row>
-    <row r="118" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A118" s="4">
+    <row r="118" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A118" s="3">
         <v>45737</v>
       </c>
       <c r="B118">
@@ -9559,7 +9561,7 @@
       <c r="G118">
         <v>150.38089244694868</v>
       </c>
-      <c r="H118" s="3">
+      <c r="H118">
         <v>150.57566380116401</v>
       </c>
       <c r="I118">
@@ -9604,7 +9606,7 @@
       <c r="V118">
         <v>61847687</v>
       </c>
-      <c r="W118" s="5">
+      <c r="W118" s="4">
         <v>24.5</v>
       </c>
       <c r="X118">
@@ -9614,8 +9616,8 @@
         <v>1387.48</v>
       </c>
     </row>
-    <row r="119" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A119" s="4">
+    <row r="119" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A119" s="3">
         <v>45741</v>
       </c>
       <c r="B119">
@@ -9636,7 +9638,7 @@
       <c r="G119">
         <v>150.38089244694868</v>
       </c>
-      <c r="H119" s="3">
+      <c r="H119">
         <v>150.57566380116401</v>
       </c>
       <c r="I119">
@@ -9681,7 +9683,7 @@
       <c r="V119">
         <v>61457421</v>
       </c>
-      <c r="W119" s="5">
+      <c r="W119" s="4">
         <v>24.5</v>
       </c>
       <c r="X119">
@@ -9691,8 +9693,8 @@
         <v>1388.54</v>
       </c>
     </row>
-    <row r="120" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A120" s="4">
+    <row r="120" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A120" s="3">
         <v>45742</v>
       </c>
       <c r="B120">
@@ -9713,7 +9715,7 @@
       <c r="G120">
         <v>150.38089244694868</v>
       </c>
-      <c r="H120" s="3">
+      <c r="H120">
         <v>150.57566380116401</v>
       </c>
       <c r="I120">
@@ -9758,7 +9760,7 @@
       <c r="V120">
         <v>61359228</v>
       </c>
-      <c r="W120" s="5">
+      <c r="W120" s="4">
         <v>24.5</v>
       </c>
       <c r="X120">
@@ -9768,8 +9770,8 @@
         <v>1392.8</v>
       </c>
     </row>
-    <row r="121" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A121" s="4">
+    <row r="121" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A121" s="3">
         <v>45743</v>
       </c>
       <c r="B121">
@@ -9790,7 +9792,7 @@
       <c r="G121">
         <v>150.38089244694868</v>
       </c>
-      <c r="H121" s="3">
+      <c r="H121">
         <v>150.57566380116401</v>
       </c>
       <c r="I121">
@@ -9835,7 +9837,7 @@
       <c r="V121">
         <v>61695734</v>
       </c>
-      <c r="W121" s="5">
+      <c r="W121" s="4">
         <v>24.5</v>
       </c>
       <c r="X121">
@@ -9845,8 +9847,8 @@
         <v>1393.86</v>
       </c>
     </row>
-    <row r="122" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A122" s="4">
+    <row r="122" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A122" s="3">
         <v>45744</v>
       </c>
       <c r="B122">
@@ -9867,7 +9869,7 @@
       <c r="G122">
         <v>150.38089244694868</v>
       </c>
-      <c r="H122" s="3">
+      <c r="H122">
         <v>150.57566380116401</v>
       </c>
       <c r="I122">
@@ -9912,7 +9914,7 @@
       <c r="V122">
         <v>61176766</v>
       </c>
-      <c r="W122" s="5">
+      <c r="W122" s="4">
         <v>24.5</v>
       </c>
       <c r="X122">
@@ -9922,8 +9924,8 @@
         <v>1394.93</v>
       </c>
     </row>
-    <row r="123" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A123" s="4">
+    <row r="123" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A123" s="3">
         <v>45747</v>
       </c>
       <c r="B123">
@@ -9944,7 +9946,7 @@
       <c r="G123">
         <v>150.38089244694868</v>
       </c>
-      <c r="H123" s="3">
+      <c r="H123">
         <v>150.57566380116401</v>
       </c>
       <c r="I123">
@@ -9989,7 +9991,7 @@
       <c r="V123">
         <v>60448422</v>
       </c>
-      <c r="W123" s="5">
+      <c r="W123" s="4">
         <v>24.5</v>
       </c>
       <c r="X123">
@@ -9999,8 +10001,8 @@
         <v>1396</v>
       </c>
     </row>
-    <row r="124" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A124" s="4">
+    <row r="124" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A124" s="3">
         <v>45748</v>
       </c>
       <c r="B124">
@@ -10021,7 +10023,7 @@
       <c r="G124">
         <v>159.11563682577949</v>
       </c>
-      <c r="H124" s="3">
+      <c r="H124">
         <v>152.73554832812366</v>
       </c>
       <c r="I124">
@@ -10066,7 +10068,7 @@
       <c r="V124">
         <v>60747233</v>
       </c>
-      <c r="W124" s="5">
+      <c r="W124" s="4">
         <v>26.3</v>
       </c>
       <c r="X124">
@@ -10076,8 +10078,8 @@
         <v>1399.2</v>
       </c>
     </row>
-    <row r="125" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A125" s="4">
+    <row r="125" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A125" s="3">
         <v>45750</v>
       </c>
       <c r="B125">
@@ -10098,7 +10100,7 @@
       <c r="G125">
         <v>159.11563682577949</v>
       </c>
-      <c r="H125" s="3">
+      <c r="H125">
         <v>152.73554832812366</v>
       </c>
       <c r="I125">
@@ -10143,7 +10145,7 @@
       <c r="V125">
         <v>60972512</v>
       </c>
-      <c r="W125" s="5">
+      <c r="W125" s="4">
         <v>26.3</v>
       </c>
       <c r="X125">
@@ -10153,8 +10155,8 @@
         <v>1400.28</v>
       </c>
     </row>
-    <row r="126" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A126" s="4">
+    <row r="126" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A126" s="3">
         <v>45751</v>
       </c>
       <c r="B126">
@@ -10175,7 +10177,7 @@
       <c r="G126">
         <v>159.11563682577949</v>
       </c>
-      <c r="H126" s="3">
+      <c r="H126">
         <v>152.73554832812366</v>
       </c>
       <c r="I126">
@@ -10220,7 +10222,7 @@
       <c r="V126">
         <v>61032427</v>
       </c>
-      <c r="W126" s="5">
+      <c r="W126" s="4">
         <v>26.3</v>
       </c>
       <c r="X126">
@@ -10230,8 +10232,8 @@
         <v>1402.42</v>
       </c>
     </row>
-    <row r="127" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A127" s="4">
+    <row r="127" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A127" s="3">
         <v>45754</v>
       </c>
       <c r="B127">
@@ -10252,7 +10254,7 @@
       <c r="G127">
         <v>159.11563682577949</v>
       </c>
-      <c r="H127" s="3">
+      <c r="H127">
         <v>152.73554832812366</v>
       </c>
       <c r="I127">
@@ -10297,7 +10299,7 @@
       <c r="V127">
         <v>60027695</v>
       </c>
-      <c r="W127" s="5">
+      <c r="W127" s="4">
         <v>26.3</v>
       </c>
       <c r="X127">
@@ -10307,8 +10309,8 @@
         <v>1403.49</v>
       </c>
     </row>
-    <row r="128" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A128" s="4">
+    <row r="128" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A128" s="3">
         <v>45755</v>
       </c>
       <c r="B128">
@@ -10329,7 +10331,7 @@
       <c r="G128">
         <v>159.11563682577949</v>
       </c>
-      <c r="H128" s="3">
+      <c r="H128">
         <v>152.73554832812366</v>
       </c>
       <c r="I128">
@@ -10374,7 +10376,7 @@
       <c r="V128">
         <v>60276056</v>
       </c>
-      <c r="W128" s="5">
+      <c r="W128" s="4">
         <v>26.3</v>
       </c>
       <c r="X128">
@@ -10384,8 +10386,8 @@
         <v>1406.72</v>
       </c>
     </row>
-    <row r="129" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A129" s="4">
+    <row r="129" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A129" s="3">
         <v>45756</v>
       </c>
       <c r="B129">
@@ -10406,7 +10408,7 @@
       <c r="G129">
         <v>159.11563682577949</v>
       </c>
-      <c r="H129" s="3">
+      <c r="H129">
         <v>152.73554832812366</v>
       </c>
       <c r="I129">
@@ -10451,7 +10453,7 @@
       <c r="V129">
         <v>59876962</v>
       </c>
-      <c r="W129" s="5">
+      <c r="W129" s="4">
         <v>26.3</v>
       </c>
       <c r="X129">
@@ -10461,8 +10463,8 @@
         <v>1407.79</v>
       </c>
     </row>
-    <row r="130" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A130" s="4">
+    <row r="130" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A130" s="3">
         <v>45757</v>
       </c>
       <c r="B130">
@@ -10483,7 +10485,7 @@
       <c r="G130">
         <v>159.11563682577949</v>
       </c>
-      <c r="H130" s="3">
+      <c r="H130">
         <v>152.73554832812366</v>
       </c>
       <c r="I130">
@@ -10528,7 +10530,7 @@
       <c r="V130">
         <v>59769029</v>
       </c>
-      <c r="W130" s="5">
+      <c r="W130" s="4">
         <v>26.3</v>
       </c>
       <c r="X130">
@@ -10538,8 +10540,8 @@
         <v>1408.87</v>
       </c>
     </row>
-    <row r="131" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A131" s="4">
+    <row r="131" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A131" s="3">
         <v>45758</v>
       </c>
       <c r="B131">
@@ -10560,7 +10562,7 @@
       <c r="G131">
         <v>159.11563682577949</v>
       </c>
-      <c r="H131" s="3">
+      <c r="H131">
         <v>152.73554832812366</v>
       </c>
       <c r="I131">
@@ -10605,7 +10607,7 @@
       <c r="V131">
         <v>59581690</v>
       </c>
-      <c r="W131" s="5">
+      <c r="W131" s="4">
         <v>26.3</v>
       </c>
       <c r="X131">
@@ -10615,8 +10617,8 @@
         <v>1409.95</v>
       </c>
     </row>
-    <row r="132" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A132" s="4">
+    <row r="132" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A132" s="3">
         <v>45761</v>
       </c>
       <c r="B132">
@@ -10637,7 +10639,7 @@
       <c r="G132">
         <v>159.11563682577949</v>
       </c>
-      <c r="H132" s="3">
+      <c r="H132">
         <v>152.73554832812366</v>
       </c>
       <c r="I132">
@@ -10682,7 +10684,7 @@
       <c r="V132">
         <v>58372212</v>
       </c>
-      <c r="W132" s="5">
+      <c r="W132" s="4">
         <v>26.3</v>
       </c>
       <c r="X132">
@@ -10692,8 +10694,8 @@
         <v>1411.03</v>
       </c>
     </row>
-    <row r="133" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A133" s="4">
+    <row r="133" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A133" s="3">
         <v>45762</v>
       </c>
       <c r="B133">
@@ -10714,7 +10716,7 @@
       <c r="G133">
         <v>159.11563682577949</v>
       </c>
-      <c r="H133" s="3">
+      <c r="H133">
         <v>152.73554832812366</v>
       </c>
       <c r="I133">
@@ -10759,7 +10761,7 @@
       <c r="V133">
         <v>58571344</v>
       </c>
-      <c r="W133" s="5">
+      <c r="W133" s="4">
         <v>26.3</v>
       </c>
       <c r="X133">
@@ -10769,8 +10771,8 @@
         <v>1414.27</v>
       </c>
     </row>
-    <row r="134" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A134" s="4">
+    <row r="134" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A134" s="3">
         <v>45763</v>
       </c>
       <c r="B134">
@@ -10791,7 +10793,7 @@
       <c r="G134">
         <v>159.11563682577949</v>
       </c>
-      <c r="H134" s="3">
+      <c r="H134">
         <v>152.73554832812366</v>
       </c>
       <c r="I134">
@@ -10836,7 +10838,7 @@
       <c r="V134">
         <v>60702532</v>
       </c>
-      <c r="W134" s="5">
+      <c r="W134" s="4">
         <v>26.3</v>
       </c>
       <c r="X134">
@@ -10846,8 +10848,8 @@
         <v>1415.35</v>
       </c>
     </row>
-    <row r="135" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A135" s="4">
+    <row r="135" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A135" s="3">
         <v>45768</v>
       </c>
       <c r="B135">
@@ -10868,7 +10870,7 @@
       <c r="G135">
         <v>159.11563682577949</v>
       </c>
-      <c r="H135" s="3">
+      <c r="H135">
         <v>152.73554832812366</v>
       </c>
       <c r="I135">
@@ -10913,7 +10915,7 @@
       <c r="V135">
         <v>58868921</v>
       </c>
-      <c r="W135" s="5">
+      <c r="W135" s="4">
         <v>26.3</v>
       </c>
       <c r="X135">
@@ -10923,8 +10925,8 @@
         <v>1417.07</v>
       </c>
     </row>
-    <row r="136" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A136" s="4">
+    <row r="136" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A136" s="3">
         <v>45769</v>
       </c>
       <c r="B136">
@@ -10945,7 +10947,7 @@
       <c r="G136">
         <v>159.11563682577949</v>
       </c>
-      <c r="H136" s="3">
+      <c r="H136">
         <v>152.73554832812366</v>
       </c>
       <c r="I136">
@@ -10990,7 +10992,7 @@
       <c r="V136">
         <v>59642287</v>
       </c>
-      <c r="W136" s="5">
+      <c r="W136" s="4">
         <v>26.3</v>
       </c>
       <c r="X136">
@@ -11000,8 +11002,8 @@
         <v>1425.68</v>
       </c>
     </row>
-    <row r="137" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A137" s="4">
+    <row r="137" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A137" s="3">
         <v>45770</v>
       </c>
       <c r="B137">
@@ -11022,7 +11024,7 @@
       <c r="G137">
         <v>159.11563682577949</v>
       </c>
-      <c r="H137" s="3">
+      <c r="H137">
         <v>152.73554832812366</v>
       </c>
       <c r="I137">
@@ -11067,7 +11069,7 @@
       <c r="V137">
         <v>60123628</v>
       </c>
-      <c r="W137" s="5">
+      <c r="W137" s="4">
         <v>26.3</v>
       </c>
       <c r="X137">
@@ -11077,8 +11079,8 @@
         <v>1427.4</v>
       </c>
     </row>
-    <row r="138" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A138" s="4">
+    <row r="138" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A138" s="3">
         <v>45771</v>
       </c>
       <c r="B138">
@@ -11099,7 +11101,7 @@
       <c r="G138">
         <v>159.11563682577949</v>
       </c>
-      <c r="H138" s="3">
+      <c r="H138">
         <v>152.73554832812366</v>
       </c>
       <c r="I138">
@@ -11144,7 +11146,7 @@
       <c r="V138">
         <v>60484057</v>
       </c>
-      <c r="W138" s="5">
+      <c r="W138" s="4">
         <v>26.3</v>
       </c>
       <c r="X138">
@@ -11154,8 +11156,8 @@
         <v>1429.13</v>
       </c>
     </row>
-    <row r="139" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A139" s="4">
+    <row r="139" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A139" s="3">
         <v>45772</v>
       </c>
       <c r="B139">
@@ -11176,7 +11178,7 @@
       <c r="G139">
         <v>159.11563682577949</v>
       </c>
-      <c r="H139" s="3">
+      <c r="H139">
         <v>152.73554832812366</v>
       </c>
       <c r="I139">
@@ -11221,7 +11223,7 @@
       <c r="V139">
         <v>60877955</v>
       </c>
-      <c r="W139" s="5">
+      <c r="W139" s="4">
         <v>26.3</v>
       </c>
       <c r="X139">
@@ -11231,8 +11233,8 @@
         <v>1430.87</v>
       </c>
     </row>
-    <row r="140" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A140" s="4">
+    <row r="140" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A140" s="3">
         <v>45775</v>
       </c>
       <c r="B140">
@@ -11253,7 +11255,7 @@
       <c r="G140">
         <v>159.11563682577949</v>
       </c>
-      <c r="H140" s="3">
+      <c r="H140">
         <v>152.73554832812366</v>
       </c>
       <c r="I140">
@@ -11298,7 +11300,7 @@
       <c r="V140">
         <v>60531385</v>
       </c>
-      <c r="W140" s="5">
+      <c r="W140" s="4">
         <v>26.3</v>
       </c>
       <c r="X140">
@@ -11308,8 +11310,8 @@
         <v>1432.6</v>
       </c>
     </row>
-    <row r="141" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A141" s="4">
+    <row r="141" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A141" s="3">
         <v>45776</v>
       </c>
       <c r="B141">
@@ -11330,7 +11332,7 @@
       <c r="G141">
         <v>159.11563682577949</v>
       </c>
-      <c r="H141" s="3">
+      <c r="H141">
         <v>152.73554832812366</v>
       </c>
       <c r="I141">
@@ -11375,7 +11377,7 @@
       <c r="V141">
         <v>60774854</v>
       </c>
-      <c r="W141" s="5">
+      <c r="W141" s="4">
         <v>26.3</v>
       </c>
       <c r="X141">
@@ -11385,8 +11387,8 @@
         <v>1437.81</v>
       </c>
     </row>
-    <row r="142" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A142" s="4">
+    <row r="142" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A142" s="3">
         <v>45777</v>
       </c>
       <c r="B142">
@@ -11407,7 +11409,7 @@
       <c r="G142">
         <v>159.11563682577949</v>
       </c>
-      <c r="H142" s="3">
+      <c r="H142">
         <v>152.73554832812366</v>
       </c>
       <c r="I142">
@@ -11452,7 +11454,7 @@
       <c r="V142">
         <v>60676157</v>
       </c>
-      <c r="W142" s="5">
+      <c r="W142" s="4">
         <v>26.3</v>
       </c>
       <c r="X142">
@@ -11462,8 +11464,8 @@
         <v>1439.56</v>
       </c>
     </row>
-    <row r="143" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A143" s="4">
+    <row r="143" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A143" s="3">
         <v>45782</v>
       </c>
       <c r="B143">
@@ -11484,7 +11486,7 @@
       <c r="G143">
         <v>165.06861023955358</v>
       </c>
-      <c r="H143" s="3">
+      <c r="H143">
         <v>152.44020690666292</v>
       </c>
       <c r="I143">
@@ -11529,7 +11531,7 @@
       <c r="V143">
         <v>59191439</v>
       </c>
-      <c r="W143" s="5">
+      <c r="W143" s="4">
         <v>20.9</v>
       </c>
       <c r="X143">
@@ -11539,8 +11541,8 @@
         <v>1441.3</v>
       </c>
     </row>
-    <row r="144" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A144" s="4">
+    <row r="144" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A144" s="3">
         <v>45783</v>
       </c>
       <c r="B144">
@@ -11561,7 +11563,7 @@
       <c r="G144">
         <v>165.06861023955358</v>
       </c>
-      <c r="H144" s="3">
+      <c r="H144">
         <v>152.44020690666292</v>
       </c>
       <c r="I144">
@@ -11606,7 +11608,7 @@
       <c r="V144">
         <v>59560647</v>
       </c>
-      <c r="W144" s="5">
+      <c r="W144" s="4">
         <v>20.9</v>
       </c>
       <c r="X144">
@@ -11616,8 +11618,8 @@
         <v>1450.05</v>
       </c>
     </row>
-    <row r="145" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A145" s="4">
+    <row r="145" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A145" s="3">
         <v>45784</v>
       </c>
       <c r="B145">
@@ -11638,7 +11640,7 @@
       <c r="G145">
         <v>165.06861023955358</v>
       </c>
-      <c r="H145" s="3">
+      <c r="H145">
         <v>152.44020690666292</v>
       </c>
       <c r="I145">
@@ -11683,7 +11685,7 @@
       <c r="V145">
         <v>59081318</v>
       </c>
-      <c r="W145" s="5">
+      <c r="W145" s="4">
         <v>20.9</v>
       </c>
       <c r="X145">
@@ -11693,8 +11695,8 @@
         <v>1451.81</v>
       </c>
     </row>
-    <row r="146" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A146" s="4">
+    <row r="146" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A146" s="3">
         <v>45785</v>
       </c>
       <c r="B146">
@@ -11715,7 +11717,7 @@
       <c r="G146">
         <v>165.06861023955358</v>
       </c>
-      <c r="H146" s="3">
+      <c r="H146">
         <v>152.44020690666292</v>
       </c>
       <c r="I146">
@@ -11760,7 +11762,7 @@
       <c r="V146">
         <v>59209974</v>
       </c>
-      <c r="W146" s="5">
+      <c r="W146" s="4">
         <v>20.9</v>
       </c>
       <c r="X146">
@@ -11770,8 +11772,8 @@
         <v>1453.57</v>
       </c>
     </row>
-    <row r="147" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A147" s="4">
+    <row r="147" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A147" s="3">
         <v>45786</v>
       </c>
       <c r="B147">
@@ -11792,7 +11794,7 @@
       <c r="G147">
         <v>165.06861023955358</v>
       </c>
-      <c r="H147" s="3">
+      <c r="H147">
         <v>152.44020690666292</v>
       </c>
       <c r="I147">
@@ -11837,7 +11839,7 @@
       <c r="V147">
         <v>59980424</v>
       </c>
-      <c r="W147" s="5">
+      <c r="W147" s="4">
         <v>20.9</v>
       </c>
       <c r="X147">
@@ -11847,8 +11849,8 @@
         <v>1455.33</v>
       </c>
     </row>
-    <row r="148" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A148" s="4">
+    <row r="148" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A148" s="3">
         <v>45789</v>
       </c>
       <c r="B148">
@@ -11869,7 +11871,7 @@
       <c r="G148">
         <v>165.06861023955358</v>
       </c>
-      <c r="H148" s="3">
+      <c r="H148">
         <v>152.44020690666292</v>
       </c>
       <c r="I148">
@@ -11914,7 +11916,7 @@
       <c r="V148">
         <v>60114867</v>
       </c>
-      <c r="W148" s="5">
+      <c r="W148" s="4">
         <v>20.9</v>
       </c>
       <c r="X148">
@@ -11924,8 +11926,8 @@
         <v>1457.1</v>
       </c>
     </row>
-    <row r="149" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A149" s="4">
+    <row r="149" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A149" s="3">
         <v>45790</v>
       </c>
       <c r="B149">
@@ -11946,7 +11948,7 @@
       <c r="G149">
         <v>165.06861023955358</v>
       </c>
-      <c r="H149" s="3">
+      <c r="H149">
         <v>152.44020690666292</v>
       </c>
       <c r="I149">
@@ -11991,7 +11993,7 @@
       <c r="V149">
         <v>60735490</v>
       </c>
-      <c r="W149" s="5">
+      <c r="W149" s="4">
         <v>20.9</v>
       </c>
       <c r="X149">
@@ -12001,8 +12003,8 @@
         <v>1462.4</v>
       </c>
     </row>
-    <row r="150" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A150" s="4">
+    <row r="150" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A150" s="3">
         <v>45791</v>
       </c>
       <c r="B150">
@@ -12023,7 +12025,7 @@
       <c r="G150">
         <v>165.06861023955358</v>
       </c>
-      <c r="H150" s="3">
+      <c r="H150">
         <v>152.44020690666292</v>
       </c>
       <c r="I150">
@@ -12068,7 +12070,7 @@
       <c r="V150">
         <v>61798142</v>
       </c>
-      <c r="W150" s="5">
+      <c r="W150" s="4">
         <v>20.9</v>
       </c>
       <c r="X150">
@@ -12078,8 +12080,8 @@
         <v>1464.17</v>
       </c>
     </row>
-    <row r="151" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A151" s="4">
+    <row r="151" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A151" s="3">
         <v>45792</v>
       </c>
       <c r="B151">
@@ -12100,7 +12102,7 @@
       <c r="G151">
         <v>165.06861023955358</v>
       </c>
-      <c r="H151" s="3">
+      <c r="H151">
         <v>152.44020690666292</v>
       </c>
       <c r="I151">
@@ -12145,7 +12147,7 @@
       <c r="V151">
         <v>62512332</v>
       </c>
-      <c r="W151" s="5">
+      <c r="W151" s="4">
         <v>20.9</v>
       </c>
       <c r="X151">
@@ -12155,8 +12157,8 @@
         <v>1465.95</v>
       </c>
     </row>
-    <row r="152" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A152" s="4">
+    <row r="152" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A152" s="3">
         <v>45793</v>
       </c>
       <c r="B152">
@@ -12177,7 +12179,7 @@
       <c r="G152">
         <v>165.06861023955358</v>
       </c>
-      <c r="H152" s="3">
+      <c r="H152">
         <v>152.44020690666292</v>
       </c>
       <c r="I152">
@@ -12222,7 +12224,7 @@
       <c r="V152">
         <v>63134903</v>
       </c>
-      <c r="W152" s="5">
+      <c r="W152" s="4">
         <v>20.9</v>
       </c>
       <c r="X152">
@@ -12232,8 +12234,8 @@
         <v>1467.72</v>
       </c>
     </row>
-    <row r="153" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A153" s="4">
+    <row r="153" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A153" s="3">
         <v>45796</v>
       </c>
       <c r="B153">
@@ -12254,7 +12256,7 @@
       <c r="G153">
         <v>165.06861023955358</v>
       </c>
-      <c r="H153" s="3">
+      <c r="H153">
         <v>152.44020690666292</v>
       </c>
       <c r="I153">
@@ -12299,7 +12301,7 @@
       <c r="V153">
         <v>63717224</v>
       </c>
-      <c r="W153" s="5">
+      <c r="W153" s="4">
         <v>20.9</v>
       </c>
       <c r="X153">
@@ -12309,8 +12311,8 @@
         <v>1469.03</v>
       </c>
     </row>
-    <row r="154" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A154" s="4">
+    <row r="154" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A154" s="3">
         <v>45797</v>
       </c>
       <c r="B154">
@@ -12331,7 +12333,7 @@
       <c r="G154">
         <v>165.06861023955358</v>
       </c>
-      <c r="H154" s="3">
+      <c r="H154">
         <v>152.44020690666292</v>
       </c>
       <c r="I154">
@@ -12376,7 +12378,7 @@
       <c r="V154">
         <v>65159049</v>
       </c>
-      <c r="W154" s="5">
+      <c r="W154" s="4">
         <v>20.9</v>
       </c>
       <c r="X154">
@@ -12386,8 +12388,8 @@
         <v>1472.96</v>
       </c>
     </row>
-    <row r="155" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A155" s="4">
+    <row r="155" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A155" s="3">
         <v>45798</v>
       </c>
       <c r="B155">
@@ -12408,7 +12410,7 @@
       <c r="G155">
         <v>165.06861023955358</v>
       </c>
-      <c r="H155" s="3">
+      <c r="H155">
         <v>152.44020690666292</v>
       </c>
       <c r="I155">
@@ -12453,7 +12455,7 @@
       <c r="V155">
         <v>65123712</v>
       </c>
-      <c r="W155" s="5">
+      <c r="W155" s="4">
         <v>20.9</v>
       </c>
       <c r="X155">
@@ -12463,8 +12465,8 @@
         <v>1474.27</v>
       </c>
     </row>
-    <row r="156" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A156" s="4">
+    <row r="156" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A156" s="3">
         <v>45799</v>
       </c>
       <c r="B156">
@@ -12485,7 +12487,7 @@
       <c r="G156">
         <v>165.06861023955358</v>
       </c>
-      <c r="H156" s="3">
+      <c r="H156">
         <v>152.44020690666292</v>
       </c>
       <c r="I156">
@@ -12530,7 +12532,7 @@
       <c r="V156">
         <v>65584515</v>
       </c>
-      <c r="W156" s="5">
+      <c r="W156" s="4">
         <v>20.9</v>
       </c>
       <c r="X156">
@@ -12540,8 +12542,8 @@
         <v>1475.59</v>
       </c>
     </row>
-    <row r="157" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A157" s="4">
+    <row r="157" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A157" s="3">
         <v>45800</v>
       </c>
       <c r="B157">
@@ -12562,7 +12564,7 @@
       <c r="G157">
         <v>165.06861023955358</v>
       </c>
-      <c r="H157" s="3">
+      <c r="H157">
         <v>152.44020690666292</v>
       </c>
       <c r="I157">
@@ -12607,7 +12609,7 @@
       <c r="V157">
         <v>67137776</v>
       </c>
-      <c r="W157" s="5">
+      <c r="W157" s="4">
         <v>20.9</v>
       </c>
       <c r="X157">
@@ -12617,8 +12619,8 @@
         <v>1476.9</v>
       </c>
     </row>
-    <row r="158" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A158" s="4">
+    <row r="158" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A158" s="3">
         <v>45803</v>
       </c>
       <c r="B158">
@@ -12630,7 +12632,7 @@
       <c r="G158">
         <v>165.06861023955358</v>
       </c>
-      <c r="H158" s="3">
+      <c r="H158">
         <v>152.44020690666292</v>
       </c>
       <c r="I158">
@@ -12675,7 +12677,7 @@
       <c r="V158">
         <v>66536952</v>
       </c>
-      <c r="W158" s="5">
+      <c r="W158" s="4">
         <v>20.9</v>
       </c>
       <c r="X158">
@@ -12685,8 +12687,8 @@
         <v>1478.22</v>
       </c>
     </row>
-    <row r="159" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A159" s="4">
+    <row r="159" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A159" s="3">
         <v>45804</v>
       </c>
       <c r="B159">
@@ -12707,7 +12709,7 @@
       <c r="G159">
         <v>165.06861023955358</v>
       </c>
-      <c r="H159" s="3">
+      <c r="H159">
         <v>152.44020690666292</v>
       </c>
       <c r="I159">
@@ -12752,7 +12754,7 @@
       <c r="V159">
         <v>66862404</v>
       </c>
-      <c r="W159" s="5">
+      <c r="W159" s="4">
         <v>20.9</v>
       </c>
       <c r="X159">
@@ -12762,8 +12764,8 @@
         <v>1482.18</v>
       </c>
     </row>
-    <row r="160" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A160" s="4">
+    <row r="160" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A160" s="3">
         <v>45805</v>
       </c>
       <c r="B160">
@@ -12784,7 +12786,7 @@
       <c r="G160">
         <v>165.06861023955358</v>
       </c>
-      <c r="H160" s="3">
+      <c r="H160">
         <v>152.44020690666292</v>
       </c>
       <c r="I160">
@@ -12829,7 +12831,7 @@
       <c r="V160">
         <v>66779369</v>
       </c>
-      <c r="W160" s="5">
+      <c r="W160" s="4">
         <v>20.9</v>
       </c>
       <c r="X160">
@@ -12839,8 +12841,8 @@
         <v>1483.5</v>
       </c>
     </row>
-    <row r="161" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A161" s="4">
+    <row r="161" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A161" s="3">
         <v>45806</v>
       </c>
       <c r="B161">
@@ -12861,7 +12863,7 @@
       <c r="G161">
         <v>165.06861023955358</v>
       </c>
-      <c r="H161" s="3">
+      <c r="H161">
         <v>152.44020690666292</v>
       </c>
       <c r="I161">
@@ -12906,7 +12908,7 @@
       <c r="V161">
         <v>66396904</v>
       </c>
-      <c r="W161" s="5">
+      <c r="W161" s="4">
         <v>20.9</v>
       </c>
       <c r="X161">
@@ -12916,8 +12918,8 @@
         <v>1484.82</v>
       </c>
     </row>
-    <row r="162" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A162" s="4">
+    <row r="162" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A162" s="3">
         <v>45807</v>
       </c>
       <c r="B162">
@@ -12938,7 +12940,7 @@
       <c r="G162">
         <v>165.06861023955358</v>
       </c>
-      <c r="H162" s="3">
+      <c r="H162">
         <v>152.44020690666292</v>
       </c>
       <c r="I162">
@@ -12983,7 +12985,7 @@
       <c r="V162">
         <v>66561850</v>
       </c>
-      <c r="W162" s="5">
+      <c r="W162" s="4">
         <v>20.9</v>
       </c>
       <c r="X162">
@@ -12993,8 +12995,8 @@
         <v>1486.14</v>
       </c>
     </row>
-    <row r="163" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A163" s="4">
+    <row r="163" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A163" s="3">
         <v>45810</v>
       </c>
       <c r="B163">
@@ -13015,7 +13017,7 @@
       <c r="G163">
         <v>156.74462959682248</v>
       </c>
-      <c r="H163" s="3">
+      <c r="H163">
         <v>151.37671847017455</v>
       </c>
       <c r="I163">
@@ -13060,7 +13062,7 @@
       <c r="V163">
         <v>66766748</v>
       </c>
-      <c r="W163" s="5">
+      <c r="W163" s="4">
         <v>20.8</v>
       </c>
       <c r="X163">
@@ -13070,8 +13072,8 @@
         <v>1487.47</v>
       </c>
     </row>
-    <row r="164" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A164" s="4">
+    <row r="164" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A164" s="3">
         <v>45811</v>
       </c>
       <c r="B164">
@@ -13092,7 +13094,7 @@
       <c r="G164">
         <v>156.74462959682248</v>
       </c>
-      <c r="H164" s="3">
+      <c r="H164">
         <v>151.37671847017455</v>
       </c>
       <c r="I164">
@@ -13137,7 +13139,7 @@
       <c r="V164">
         <v>66997656</v>
       </c>
-      <c r="W164" s="5">
+      <c r="W164" s="4">
         <v>20.8</v>
       </c>
       <c r="X164">
@@ -13147,8 +13149,8 @@
         <v>1491.45</v>
       </c>
     </row>
-    <row r="165" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A165" s="4">
+    <row r="165" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A165" s="3">
         <v>45812</v>
       </c>
       <c r="B165">
@@ -13169,7 +13171,7 @@
       <c r="G165">
         <v>156.74462959682248</v>
       </c>
-      <c r="H165" s="3">
+      <c r="H165">
         <v>151.37671847017455</v>
       </c>
       <c r="I165">
@@ -13214,7 +13216,7 @@
       <c r="V165">
         <v>66698354</v>
       </c>
-      <c r="W165" s="5">
+      <c r="W165" s="4">
         <v>20.8</v>
       </c>
       <c r="X165">
@@ -13224,8 +13226,8 @@
         <v>1492.78</v>
       </c>
     </row>
-    <row r="166" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A166" s="4">
+    <row r="166" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A166" s="3">
         <v>45813</v>
       </c>
       <c r="B166">
@@ -13246,7 +13248,7 @@
       <c r="G166">
         <v>156.74462959682248</v>
       </c>
-      <c r="H166" s="3">
+      <c r="H166">
         <v>151.37671847017455</v>
       </c>
       <c r="I166">
@@ -13291,7 +13293,7 @@
       <c r="V166">
         <v>66798093</v>
       </c>
-      <c r="W166" s="5">
+      <c r="W166" s="4">
         <v>20.8</v>
       </c>
       <c r="X166">
@@ -13301,8 +13303,8 @@
         <v>1494.11</v>
       </c>
     </row>
-    <row r="167" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A167" s="4">
+    <row r="167" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A167" s="3">
         <v>45814</v>
       </c>
       <c r="B167">
@@ -13323,7 +13325,7 @@
       <c r="G167">
         <v>156.74462959682248</v>
       </c>
-      <c r="H167" s="3">
+      <c r="H167">
         <v>151.37671847017455</v>
       </c>
       <c r="I167">
@@ -13368,7 +13370,7 @@
       <c r="V167">
         <v>67012386</v>
       </c>
-      <c r="W167" s="5">
+      <c r="W167" s="4">
         <v>20.8</v>
       </c>
       <c r="X167">
@@ -13378,8 +13380,8 @@
         <v>1495.44</v>
       </c>
     </row>
-    <row r="168" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A168" s="4">
+    <row r="168" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A168" s="3">
         <v>45817</v>
       </c>
       <c r="B168">
@@ -13400,7 +13402,7 @@
       <c r="G168">
         <v>156.74462959682248</v>
       </c>
-      <c r="H168" s="3">
+      <c r="H168">
         <v>151.37671847017455</v>
       </c>
       <c r="I168">
@@ -13445,7 +13447,7 @@
       <c r="V168">
         <v>66325104</v>
       </c>
-      <c r="W168" s="5">
+      <c r="W168" s="4">
         <v>20.8</v>
       </c>
       <c r="X168">
@@ -13455,8 +13457,8 @@
         <v>1496.77</v>
       </c>
     </row>
-    <row r="169" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A169" s="4">
+    <row r="169" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A169" s="3">
         <v>45818</v>
       </c>
       <c r="B169">
@@ -13477,7 +13479,7 @@
       <c r="G169">
         <v>156.74462959682248</v>
       </c>
-      <c r="H169" s="3">
+      <c r="H169">
         <v>151.37671847017455</v>
       </c>
       <c r="I169">
@@ -13522,7 +13524,7 @@
       <c r="V169">
         <v>66914412</v>
       </c>
-      <c r="W169" s="5">
+      <c r="W169" s="4">
         <v>20.8</v>
       </c>
       <c r="X169">
@@ -13532,8 +13534,8 @@
         <v>1500.78</v>
       </c>
     </row>
-    <row r="170" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A170" s="4">
+    <row r="170" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A170" s="3">
         <v>45819</v>
       </c>
       <c r="B170">
@@ -13554,7 +13556,7 @@
       <c r="G170">
         <v>156.74462959682248</v>
       </c>
-      <c r="H170" s="3">
+      <c r="H170">
         <v>151.37671847017455</v>
       </c>
       <c r="I170">
@@ -13599,7 +13601,7 @@
       <c r="V170">
         <v>67089108</v>
       </c>
-      <c r="W170" s="5">
+      <c r="W170" s="4">
         <v>20.8</v>
       </c>
       <c r="X170">
@@ -13609,8 +13611,8 @@
         <v>1502.11</v>
       </c>
     </row>
-    <row r="171" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A171" s="4">
+    <row r="171" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A171" s="3">
         <v>45820</v>
       </c>
       <c r="B171">
@@ -13631,7 +13633,7 @@
       <c r="G171">
         <v>156.74462959682248</v>
       </c>
-      <c r="H171" s="3">
+      <c r="H171">
         <v>151.37671847017455</v>
       </c>
       <c r="I171">
@@ -13676,7 +13678,7 @@
       <c r="V171">
         <v>67834507</v>
       </c>
-      <c r="W171" s="5">
+      <c r="W171" s="4">
         <v>20.8</v>
       </c>
       <c r="X171">
@@ -13686,8 +13688,8 @@
         <v>1503.45</v>
       </c>
     </row>
-    <row r="172" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A172" s="4">
+    <row r="172" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A172" s="3">
         <v>45821</v>
       </c>
       <c r="B172">
@@ -13708,7 +13710,7 @@
       <c r="G172">
         <v>156.74462959682248</v>
       </c>
-      <c r="H172" s="3">
+      <c r="H172">
         <v>151.37671847017455</v>
       </c>
       <c r="I172">
@@ -13753,7 +13755,7 @@
       <c r="V172">
         <v>69410420</v>
       </c>
-      <c r="W172" s="5">
+      <c r="W172" s="4">
         <v>20.8</v>
       </c>
       <c r="X172">
@@ -13763,8 +13765,8 @@
         <v>1504.79</v>
       </c>
     </row>
-    <row r="173" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A173" s="4">
+    <row r="173" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A173" s="3">
         <v>45825</v>
       </c>
       <c r="B173">
@@ -13785,7 +13787,7 @@
       <c r="G173">
         <v>156.74462959682248</v>
       </c>
-      <c r="H173" s="3">
+      <c r="H173">
         <v>151.37671847017455</v>
       </c>
       <c r="I173">
@@ -13830,7 +13832,7 @@
       <c r="V173">
         <v>68670144</v>
       </c>
-      <c r="W173" s="5">
+      <c r="W173" s="4">
         <v>20.8</v>
       </c>
       <c r="X173">
@@ -13840,8 +13842,8 @@
         <v>1506.13</v>
       </c>
     </row>
-    <row r="174" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A174" s="4">
+    <row r="174" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A174" s="3">
         <v>45826</v>
       </c>
       <c r="B174">
@@ -13862,7 +13864,7 @@
       <c r="G174">
         <v>156.74462959682248</v>
       </c>
-      <c r="H174" s="3">
+      <c r="H174">
         <v>151.37671847017455</v>
       </c>
       <c r="I174">
@@ -13907,7 +13909,7 @@
       <c r="V174">
         <v>68952768</v>
       </c>
-      <c r="W174" s="5">
+      <c r="W174" s="4">
         <v>20.8</v>
       </c>
       <c r="X174">
@@ -13917,8 +13919,8 @@
         <v>1510.32</v>
       </c>
     </row>
-    <row r="175" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A175" s="4">
+    <row r="175" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A175" s="3">
         <v>45827</v>
       </c>
       <c r="B175">
@@ -13930,7 +13932,7 @@
       <c r="G175">
         <v>156.74462959682248</v>
       </c>
-      <c r="H175" s="3">
+      <c r="H175">
         <v>151.37671847017455</v>
       </c>
       <c r="I175">
@@ -13975,7 +13977,7 @@
       <c r="V175">
         <v>69927771</v>
       </c>
-      <c r="W175" s="5">
+      <c r="W175" s="4">
         <v>20.8</v>
       </c>
       <c r="X175">
@@ -13985,8 +13987,8 @@
         <v>1511.07</v>
       </c>
     </row>
-    <row r="176" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A176" s="4">
+    <row r="176" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A176" s="3">
         <v>45831</v>
       </c>
       <c r="B176">
@@ -14007,7 +14009,7 @@
       <c r="G176">
         <v>156.74462959682248</v>
       </c>
-      <c r="H176" s="3">
+      <c r="H176">
         <v>151.37671847017455</v>
       </c>
       <c r="I176">
@@ -14052,7 +14054,7 @@
       <c r="V176">
         <v>68098027</v>
       </c>
-      <c r="W176" s="5">
+      <c r="W176" s="4">
         <v>20.8</v>
       </c>
       <c r="X176">
@@ -14062,8 +14064,8 @@
         <v>1511.82</v>
       </c>
     </row>
-    <row r="177" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A177" s="4">
+    <row r="177" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A177" s="3">
         <v>45832</v>
       </c>
       <c r="B177">
@@ -14084,7 +14086,7 @@
       <c r="G177">
         <v>156.74462959682248</v>
       </c>
-      <c r="H177" s="3">
+      <c r="H177">
         <v>151.37671847017455</v>
       </c>
       <c r="I177">
@@ -14129,7 +14131,7 @@
       <c r="V177">
         <v>69153079</v>
       </c>
-      <c r="W177" s="5">
+      <c r="W177" s="4">
         <v>20.8</v>
       </c>
       <c r="X177">
@@ -14139,8 +14141,8 @@
         <v>1514.82</v>
       </c>
     </row>
-    <row r="178" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A178" s="4">
+    <row r="178" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A178" s="3">
         <v>45833</v>
       </c>
       <c r="B178">
@@ -14161,7 +14163,7 @@
       <c r="G178">
         <v>156.74462959682248</v>
       </c>
-      <c r="H178" s="3">
+      <c r="H178">
         <v>151.37671847017455</v>
       </c>
       <c r="I178">
@@ -14206,7 +14208,7 @@
       <c r="V178">
         <v>69008983</v>
       </c>
-      <c r="W178" s="5">
+      <c r="W178" s="4">
         <v>20.8</v>
       </c>
       <c r="X178">
@@ -14216,8 +14218,8 @@
         <v>1515.57</v>
       </c>
     </row>
-    <row r="179" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A179" s="4">
+    <row r="179" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A179" s="3">
         <v>45834</v>
       </c>
       <c r="B179">
@@ -14238,7 +14240,7 @@
       <c r="G179">
         <v>156.74462959682248</v>
       </c>
-      <c r="H179" s="3">
+      <c r="H179">
         <v>151.37671847017455</v>
       </c>
       <c r="I179">
@@ -14283,7 +14285,7 @@
       <c r="V179">
         <v>69362229</v>
       </c>
-      <c r="W179" s="5">
+      <c r="W179" s="4">
         <v>20.8</v>
       </c>
       <c r="X179">
@@ -14293,8 +14295,8 @@
         <v>1516.33</v>
       </c>
     </row>
-    <row r="180" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A180" s="4">
+    <row r="180" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A180" s="3">
         <v>45835</v>
       </c>
       <c r="B180">
@@ -14315,7 +14317,7 @@
       <c r="G180">
         <v>156.74462959682248</v>
       </c>
-      <c r="H180" s="3">
+      <c r="H180">
         <v>151.37671847017455</v>
       </c>
       <c r="I180">
@@ -14360,7 +14362,7 @@
       <c r="V180">
         <v>69837923</v>
       </c>
-      <c r="W180" s="5">
+      <c r="W180" s="4">
         <v>20.8</v>
       </c>
       <c r="X180">
@@ -14370,8 +14372,8 @@
         <v>1517.08</v>
       </c>
     </row>
-    <row r="181" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A181" s="4">
+    <row r="181" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A181" s="3">
         <v>45838</v>
       </c>
       <c r="B181">
@@ -14389,7 +14391,6 @@
       <c r="F181">
         <v>295.40600000000001</v>
       </c>
-      <c r="H181" s="3"/>
       <c r="J181">
         <v>1217.8699999999999</v>
       </c>
@@ -14429,7 +14430,7 @@
       <c r="V181">
         <v>68364120</v>
       </c>
-      <c r="W181" s="5">
+      <c r="W181" s="4">
         <v>20.8</v>
       </c>
       <c r="X181">
@@ -14439,8 +14440,8 @@
         <v>1517.83</v>
       </c>
     </row>
-    <row r="182" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A182" s="4">
+    <row r="182" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A182" s="3">
         <v>45839</v>
       </c>
       <c r="B182">
@@ -14458,7 +14459,6 @@
       <c r="F182">
         <v>289.41399999999999</v>
       </c>
-      <c r="H182" s="3"/>
       <c r="J182">
         <v>1237.18</v>
       </c>
@@ -14498,7 +14498,7 @@
       <c r="V182">
         <v>68720398</v>
       </c>
-      <c r="W182" s="5">
+      <c r="W182" s="4">
         <v>21.1</v>
       </c>
       <c r="X182">
@@ -14508,8 +14508,8 @@
         <v>1520.09</v>
       </c>
     </row>
-    <row r="183" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A183" s="4">
+    <row r="183" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A183" s="3">
         <v>45840</v>
       </c>
       <c r="B183">
@@ -14527,7 +14527,6 @@
       <c r="F183">
         <v>288.12900000000002</v>
       </c>
-      <c r="H183" s="3"/>
       <c r="J183">
         <v>1248.43</v>
       </c>
@@ -14567,7 +14566,7 @@
       <c r="V183">
         <v>69106372</v>
       </c>
-      <c r="W183" s="5">
+      <c r="W183" s="4">
         <v>21.1</v>
       </c>
       <c r="X183">
@@ -14577,8 +14576,8 @@
         <v>1520.85</v>
       </c>
     </row>
-    <row r="184" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A184" s="4">
+    <row r="184" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A184" s="3">
         <v>45841</v>
       </c>
       <c r="B184">
@@ -14596,7 +14595,6 @@
       <c r="F184">
         <v>279.47899999999998</v>
       </c>
-      <c r="H184" s="3"/>
       <c r="J184">
         <v>1245.8499999999999</v>
       </c>
@@ -14636,7 +14634,7 @@
       <c r="V184">
         <v>69720866</v>
       </c>
-      <c r="W184" s="5">
+      <c r="W184" s="4">
         <v>21.1</v>
       </c>
       <c r="X184">
@@ -14646,8 +14644,8 @@
         <v>1521.6</v>
       </c>
     </row>
-    <row r="185" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A185" s="4">
+    <row r="185" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A185" s="3">
         <v>45842</v>
       </c>
       <c r="B185">
@@ -14656,7 +14654,6 @@
       <c r="C185">
         <v>2078697.04</v>
       </c>
-      <c r="H185" s="3"/>
       <c r="J185">
         <v>1260.3599999999999</v>
       </c>
@@ -14696,7 +14693,7 @@
       <c r="V185">
         <v>69814971</v>
       </c>
-      <c r="W185" s="5">
+      <c r="W185" s="4">
         <v>21.1</v>
       </c>
       <c r="X185">
@@ -14706,8 +14703,8 @@
         <v>1522.36</v>
       </c>
     </row>
-    <row r="186" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A186" s="4">
+    <row r="186" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A186" s="3">
         <v>45845</v>
       </c>
       <c r="B186">
@@ -14725,7 +14722,6 @@
       <c r="F186">
         <v>276.363</v>
       </c>
-      <c r="H186" s="3"/>
       <c r="J186">
         <v>1282.47</v>
       </c>
@@ -14765,7 +14761,7 @@
       <c r="V186">
         <v>69525283</v>
       </c>
-      <c r="W186" s="5">
+      <c r="W186" s="4">
         <v>21.1</v>
       </c>
       <c r="X186">
@@ -14775,8 +14771,8 @@
         <v>1523.11</v>
       </c>
     </row>
-    <row r="187" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A187" s="4">
+    <row r="187" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A187" s="3">
         <v>45846</v>
       </c>
       <c r="B187">
@@ -14794,7 +14790,6 @@
       <c r="F187">
         <v>283.05200000000002</v>
       </c>
-      <c r="H187" s="3"/>
       <c r="J187">
         <v>1276.79</v>
       </c>
@@ -14834,7 +14829,7 @@
       <c r="V187">
         <v>70145298</v>
       </c>
-      <c r="W187" s="5">
+      <c r="W187" s="4">
         <v>21.1</v>
       </c>
       <c r="X187">
@@ -14844,8 +14839,8 @@
         <v>1525.38</v>
       </c>
     </row>
-    <row r="188" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A188" s="4">
+    <row r="188" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A188" s="3">
         <v>45848</v>
       </c>
       <c r="B188">
@@ -14863,7 +14858,6 @@
       <c r="F188">
         <v>282.60599999999999</v>
       </c>
-      <c r="H188" s="3"/>
       <c r="J188">
         <v>1279.22</v>
       </c>
@@ -14903,7 +14897,7 @@
       <c r="V188">
         <v>69825295</v>
       </c>
-      <c r="W188" s="5">
+      <c r="W188" s="4">
         <v>21.1</v>
       </c>
       <c r="X188">
@@ -14913,8 +14907,8 @@
         <v>1526.14</v>
       </c>
     </row>
-    <row r="189" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A189" s="4">
+    <row r="189" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A189" s="3">
         <v>45849</v>
       </c>
       <c r="B189">
@@ -14932,7 +14926,6 @@
       <c r="F189">
         <v>280.23099999999999</v>
       </c>
-      <c r="H189" s="3"/>
       <c r="J189">
         <v>1280.8499999999999</v>
       </c>
@@ -14972,7 +14965,7 @@
       <c r="V189">
         <v>70652363</v>
       </c>
-      <c r="W189" s="5">
+      <c r="W189" s="4">
         <v>21.1</v>
       </c>
       <c r="X189">
@@ -14982,8 +14975,8 @@
         <v>1527.66</v>
       </c>
     </row>
-    <row r="190" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A190" s="4">
+    <row r="190" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A190" s="3">
         <v>45852</v>
       </c>
       <c r="B190">
@@ -15001,7 +14994,6 @@
       <c r="F190">
         <v>282.94900000000001</v>
       </c>
-      <c r="H190" s="3"/>
       <c r="J190">
         <v>1291.23</v>
       </c>
@@ -15041,7 +15033,7 @@
       <c r="V190">
         <v>70455270</v>
       </c>
-      <c r="W190" s="5">
+      <c r="W190" s="4">
         <v>21.1</v>
       </c>
       <c r="X190">
@@ -15051,8 +15043,8 @@
         <v>1528.41</v>
       </c>
     </row>
-    <row r="191" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A191" s="4">
+    <row r="191" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A191" s="3">
         <v>45853</v>
       </c>
       <c r="B191">
@@ -15070,7 +15062,6 @@
       <c r="F191">
         <v>278.93099999999998</v>
       </c>
-      <c r="H191" s="3"/>
       <c r="J191">
         <v>1288.17</v>
       </c>
@@ -15110,7 +15101,7 @@
       <c r="V191">
         <v>72199381</v>
       </c>
-      <c r="W191" s="5">
+      <c r="W191" s="4">
         <v>21.1</v>
       </c>
       <c r="X191">
@@ -15120,8 +15111,8 @@
         <v>1530.69</v>
       </c>
     </row>
-    <row r="192" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A192" s="4">
+    <row r="192" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A192" s="3">
         <v>45854</v>
       </c>
       <c r="B192">
@@ -15139,7 +15130,6 @@
       <c r="F192">
         <v>285.221</v>
       </c>
-      <c r="H192" s="3"/>
       <c r="J192">
         <v>1278.6199999999999</v>
       </c>
@@ -15179,7 +15169,7 @@
       <c r="V192">
         <v>73553206</v>
       </c>
-      <c r="W192" s="5">
+      <c r="W192" s="4">
         <v>21.1</v>
       </c>
       <c r="X192">
@@ -15189,8 +15179,8 @@
         <v>1531.45</v>
       </c>
     </row>
-    <row r="193" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A193" s="4">
+    <row r="193" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A193" s="3">
         <v>45855</v>
       </c>
       <c r="B193">
@@ -15208,7 +15198,6 @@
       <c r="F193">
         <v>284.25</v>
       </c>
-      <c r="H193" s="3"/>
       <c r="J193">
         <v>1289.98</v>
       </c>
@@ -15248,7 +15237,7 @@
       <c r="V193">
         <v>73992627</v>
       </c>
-      <c r="W193" s="5">
+      <c r="W193" s="4">
         <v>21.1</v>
       </c>
       <c r="X193">
@@ -15258,8 +15247,8 @@
         <v>1532.24</v>
       </c>
     </row>
-    <row r="194" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A194" s="4">
+    <row r="194" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A194" s="3">
         <v>45856</v>
       </c>
       <c r="B194">
@@ -15277,7 +15266,6 @@
       <c r="F194">
         <v>283.553</v>
       </c>
-      <c r="H194" s="3"/>
       <c r="J194">
         <v>1307.33</v>
       </c>
@@ -15317,7 +15305,7 @@
       <c r="V194">
         <v>74831772</v>
       </c>
-      <c r="W194" s="5">
+      <c r="W194" s="4">
         <v>21.1</v>
       </c>
       <c r="X194">
@@ -15327,8 +15315,8 @@
         <v>1533.02</v>
       </c>
     </row>
-    <row r="195" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A195" s="4">
+    <row r="195" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A195" s="3">
         <v>45859</v>
       </c>
       <c r="B195">
@@ -15346,7 +15334,6 @@
       <c r="F195">
         <v>281.46800000000002</v>
       </c>
-      <c r="H195" s="3"/>
       <c r="J195">
         <v>1298.51</v>
       </c>
@@ -15386,7 +15373,7 @@
       <c r="V195">
         <v>74862530</v>
       </c>
-      <c r="W195" s="5">
+      <c r="W195" s="4">
         <v>21.1</v>
       </c>
       <c r="X195">
@@ -15396,8 +15383,8 @@
         <v>1533.81</v>
       </c>
     </row>
-    <row r="196" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A196" s="4">
+    <row r="196" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A196" s="3">
         <v>45860</v>
       </c>
       <c r="B196">
@@ -15415,7 +15402,6 @@
       <c r="F196">
         <v>283.738</v>
       </c>
-      <c r="H196" s="3"/>
       <c r="J196">
         <v>1278.32</v>
       </c>
@@ -15455,7 +15441,7 @@
       <c r="V196">
         <v>75029138</v>
       </c>
-      <c r="W196" s="5">
+      <c r="W196" s="4">
         <v>21.1</v>
       </c>
       <c r="X196">
@@ -15465,8 +15451,8 @@
         <v>1536.16</v>
       </c>
     </row>
-    <row r="197" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A197" s="4">
+    <row r="197" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A197" s="3">
         <v>45861</v>
       </c>
       <c r="B197">
@@ -15484,7 +15470,6 @@
       <c r="F197">
         <v>279.57499999999999</v>
       </c>
-      <c r="H197" s="3"/>
       <c r="J197">
         <v>1277.43</v>
       </c>
@@ -15524,7 +15509,7 @@
       <c r="V197">
         <v>74446378</v>
       </c>
-      <c r="W197" s="5">
+      <c r="W197" s="4">
         <v>21.1</v>
       </c>
       <c r="X197">
@@ -15534,8 +15519,8 @@
         <v>1536.95</v>
       </c>
     </row>
-    <row r="198" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A198" s="4">
+    <row r="198" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A198" s="3">
         <v>45862</v>
       </c>
       <c r="B198">
@@ -15553,7 +15538,6 @@
       <c r="F198">
         <v>276.76900000000001</v>
       </c>
-      <c r="H198" s="3"/>
       <c r="J198">
         <v>1284.92</v>
       </c>
@@ -15593,7 +15577,7 @@
       <c r="V198">
         <v>74671826</v>
       </c>
-      <c r="W198" s="5">
+      <c r="W198" s="4">
         <v>21.1</v>
       </c>
       <c r="X198">
@@ -15603,8 +15587,8 @@
         <v>1537.74</v>
       </c>
     </row>
-    <row r="199" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A199" s="4">
+    <row r="199" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A199" s="3">
         <v>45863</v>
       </c>
       <c r="B199">
@@ -15622,7 +15606,6 @@
       <c r="F199">
         <v>277.04500000000002</v>
       </c>
-      <c r="H199" s="3"/>
       <c r="J199">
         <v>1300.1400000000001</v>
       </c>
@@ -15662,7 +15645,7 @@
       <c r="V199">
         <v>74514326</v>
       </c>
-      <c r="W199" s="5">
+      <c r="W199" s="4">
         <v>21.1</v>
       </c>
       <c r="X199">
@@ -15672,8 +15655,8 @@
         <v>1538.52</v>
       </c>
     </row>
-    <row r="200" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A200" s="4">
+    <row r="200" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A200" s="3">
         <v>45866</v>
       </c>
       <c r="B200">
@@ -15691,7 +15674,6 @@
       <c r="F200">
         <v>271.93099999999998</v>
       </c>
-      <c r="H200" s="3"/>
       <c r="J200">
         <v>1305.1099999999999</v>
       </c>
@@ -15731,7 +15713,7 @@
       <c r="V200">
         <v>73483280</v>
       </c>
-      <c r="W200" s="5">
+      <c r="W200" s="4">
         <v>21.1</v>
       </c>
       <c r="X200">
@@ -15741,8 +15723,8 @@
         <v>1539.31</v>
       </c>
     </row>
-    <row r="201" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A201" s="4">
+    <row r="201" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A201" s="3">
         <v>45867</v>
       </c>
       <c r="B201">
@@ -15760,7 +15742,6 @@
       <c r="F201">
         <v>277.03800000000001</v>
       </c>
-      <c r="H201" s="3"/>
       <c r="J201">
         <v>1305.05</v>
       </c>
@@ -15800,7 +15781,7 @@
       <c r="V201">
         <v>73925693</v>
       </c>
-      <c r="W201" s="5">
+      <c r="W201" s="4">
         <v>21.1</v>
       </c>
       <c r="X201">
@@ -15810,8 +15791,8 @@
         <v>1541.68</v>
       </c>
     </row>
-    <row r="202" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A202" s="4">
+    <row r="202" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A202" s="3">
         <v>45868</v>
       </c>
       <c r="B202">
@@ -15829,7 +15810,6 @@
       <c r="F202">
         <v>273.45</v>
       </c>
-      <c r="H202" s="3"/>
       <c r="J202">
         <v>1325.63</v>
       </c>
@@ -15869,7 +15849,7 @@
       <c r="V202">
         <v>72431705</v>
       </c>
-      <c r="W202" s="5">
+      <c r="W202" s="4">
         <v>21.1</v>
       </c>
       <c r="X202">
@@ -15879,8 +15859,8 @@
         <v>1542.47</v>
       </c>
     </row>
-    <row r="203" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A203" s="4">
+    <row r="203" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A203" s="3">
         <v>45869</v>
       </c>
       <c r="B203">
@@ -15898,7 +15878,6 @@
       <c r="F203">
         <v>271.58499999999998</v>
       </c>
-      <c r="H203" s="3"/>
       <c r="J203">
         <v>1385.56</v>
       </c>
@@ -15938,7 +15917,7 @@
       <c r="V203">
         <v>71820574</v>
       </c>
-      <c r="W203" s="5">
+      <c r="W203" s="4">
         <v>21.1</v>
       </c>
       <c r="X203">
@@ -15948,8 +15927,8 @@
         <v>1543.26</v>
       </c>
     </row>
-    <row r="204" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A204" s="4">
+    <row r="204" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A204" s="3">
         <v>45870</v>
       </c>
       <c r="B204">
@@ -15967,7 +15946,6 @@
       <c r="F204">
         <v>286.166</v>
       </c>
-      <c r="H204" s="3"/>
       <c r="J204">
         <v>1375.79</v>
       </c>
@@ -16007,7 +15985,7 @@
       <c r="V204">
         <v>71921359</v>
       </c>
-      <c r="W204" s="5">
+      <c r="W204" s="4">
         <v>20.9</v>
       </c>
       <c r="X204">
@@ -16017,8 +15995,8 @@
         <v>1544.05</v>
       </c>
     </row>
-    <row r="205" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A205" s="4">
+    <row r="205" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A205" s="3">
         <v>45873</v>
       </c>
       <c r="B205">
@@ -16036,7 +16014,6 @@
       <c r="F205">
         <v>282.16199999999998</v>
       </c>
-      <c r="H205" s="3"/>
       <c r="J205">
         <v>1372.68</v>
       </c>
@@ -16076,7 +16053,7 @@
       <c r="V205">
         <v>71205062</v>
       </c>
-      <c r="W205" s="5">
+      <c r="W205" s="4">
         <v>20.9</v>
       </c>
       <c r="X205">
@@ -16086,8 +16063,8 @@
         <v>1544.84</v>
       </c>
     </row>
-    <row r="206" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A206" s="4">
+    <row r="206" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A206" s="3">
         <v>45874</v>
       </c>
       <c r="B206">
@@ -16105,7 +16082,6 @@
       <c r="F206">
         <v>279.74700000000001</v>
       </c>
-      <c r="H206" s="3"/>
       <c r="J206">
         <v>1355.58</v>
       </c>
@@ -16145,7 +16121,7 @@
       <c r="V206">
         <v>71905845</v>
       </c>
-      <c r="W206" s="5">
+      <c r="W206" s="4">
         <v>20.9</v>
       </c>
       <c r="X206">
@@ -16155,8 +16131,8 @@
         <v>1547.21</v>
       </c>
     </row>
-    <row r="207" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A207" s="4">
+    <row r="207" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A207" s="3">
         <v>45875</v>
       </c>
       <c r="B207">
@@ -16174,7 +16150,6 @@
       <c r="F207">
         <v>278.59500000000003</v>
       </c>
-      <c r="H207" s="3"/>
       <c r="J207">
         <v>1346.52</v>
       </c>
@@ -16214,7 +16189,7 @@
       <c r="V207">
         <v>71391879</v>
       </c>
-      <c r="W207" s="5">
+      <c r="W207" s="4">
         <v>20.9</v>
       </c>
       <c r="X207">
@@ -16224,8 +16199,8 @@
         <v>1548.01</v>
       </c>
     </row>
-    <row r="208" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A208" s="4">
+    <row r="208" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A208" s="3">
         <v>45876</v>
       </c>
       <c r="B208">
@@ -16243,7 +16218,6 @@
       <c r="F208">
         <v>278.59500000000003</v>
       </c>
-      <c r="H208" s="3"/>
       <c r="J208">
         <v>1339.62</v>
       </c>
@@ -16283,7 +16257,7 @@
       <c r="V208">
         <v>71461313</v>
       </c>
-      <c r="W208" s="5">
+      <c r="W208" s="4">
         <v>20.9</v>
       </c>
       <c r="X208">
@@ -16293,8 +16267,8 @@
         <v>1548.8</v>
       </c>
     </row>
-    <row r="209" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A209" s="4">
+    <row r="209" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A209" s="3">
         <v>45877</v>
       </c>
       <c r="B209">
@@ -16312,7 +16286,6 @@
       <c r="F209">
         <v>271.14699999999999</v>
       </c>
-      <c r="H209" s="3"/>
       <c r="J209">
         <v>1337.04</v>
       </c>
@@ -16352,7 +16325,7 @@
       <c r="V209">
         <v>72016538</v>
       </c>
-      <c r="W209" s="5">
+      <c r="W209" s="4">
         <v>20.9</v>
       </c>
       <c r="X209">
@@ -16362,8 +16335,8 @@
         <v>1549.59</v>
       </c>
     </row>
-    <row r="210" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A210" s="4">
+    <row r="210" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A210" s="3">
         <v>45880</v>
       </c>
       <c r="B210">
@@ -16381,7 +16354,6 @@
       <c r="F210">
         <v>269.49</v>
       </c>
-      <c r="H210" s="3"/>
       <c r="J210">
         <v>1339.16</v>
       </c>
@@ -16421,7 +16393,7 @@
       <c r="V210">
         <v>70354053</v>
       </c>
-      <c r="W210" s="5">
+      <c r="W210" s="4">
         <v>20.9</v>
       </c>
       <c r="X210">
@@ -16431,8 +16403,8 @@
         <v>1550.39</v>
       </c>
     </row>
-    <row r="211" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A211" s="4">
+    <row r="211" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A211" s="3">
         <v>45881</v>
       </c>
       <c r="B211">
@@ -16450,7 +16422,6 @@
       <c r="F211">
         <v>266.73099999999999</v>
       </c>
-      <c r="H211" s="3"/>
       <c r="J211">
         <v>1330.76</v>
       </c>
@@ -16490,7 +16461,7 @@
       <c r="V211">
         <v>70812268</v>
       </c>
-      <c r="W211" s="5">
+      <c r="W211" s="4">
         <v>20.9</v>
       </c>
       <c r="X211">
@@ -16500,8 +16471,8 @@
         <v>1552.77</v>
       </c>
     </row>
-    <row r="212" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A212" s="4">
+    <row r="212" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A212" s="3">
         <v>45882</v>
       </c>
       <c r="B212">
@@ -16519,7 +16490,6 @@
       <c r="F212">
         <v>265.57499999999999</v>
       </c>
-      <c r="H212" s="3"/>
       <c r="J212">
         <v>1328.23</v>
       </c>
@@ -16559,7 +16529,7 @@
       <c r="V212">
         <v>70654902</v>
       </c>
-      <c r="W212" s="5">
+      <c r="W212" s="4">
         <v>20.9</v>
       </c>
       <c r="X212">
@@ -16569,8 +16539,8 @@
         <v>1553.57</v>
       </c>
     </row>
-    <row r="213" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A213" s="4">
+    <row r="213" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A213" s="3">
         <v>45883</v>
       </c>
       <c r="B213">
@@ -16588,7 +16558,6 @@
       <c r="F213">
         <v>261.66800000000001</v>
       </c>
-      <c r="H213" s="3"/>
       <c r="J213">
         <v>1311.41</v>
       </c>
@@ -16628,7 +16597,7 @@
       <c r="V213">
         <v>71700250</v>
       </c>
-      <c r="W213" s="5">
+      <c r="W213" s="4">
         <v>20.9</v>
       </c>
       <c r="X213">
@@ -16638,8 +16607,8 @@
         <v>1554.36</v>
       </c>
     </row>
-    <row r="214" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A214" s="4">
+    <row r="214" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A214" s="3">
         <v>45887</v>
       </c>
       <c r="B214">
@@ -16657,7 +16626,6 @@
       <c r="F214">
         <v>258.54700000000003</v>
       </c>
-      <c r="H214" s="3"/>
       <c r="J214">
         <v>1314.24</v>
       </c>
@@ -16697,7 +16665,7 @@
       <c r="V214">
         <v>72238491</v>
       </c>
-      <c r="W214" s="5">
+      <c r="W214" s="4">
         <v>20.9</v>
       </c>
       <c r="X214">
@@ -16707,8 +16675,8 @@
         <v>1555.16</v>
       </c>
     </row>
-    <row r="215" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A215" s="4">
+    <row r="215" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A215" s="3">
         <v>45888</v>
       </c>
       <c r="B215">
@@ -16726,7 +16694,6 @@
       <c r="F215">
         <v>259.75099999999998</v>
       </c>
-      <c r="H215" s="3"/>
       <c r="J215">
         <v>1312.95</v>
       </c>
@@ -16766,7 +16733,7 @@
       <c r="V215">
         <v>73699986</v>
       </c>
-      <c r="W215" s="5">
+      <c r="W215" s="4">
         <v>20.9</v>
       </c>
       <c r="X215">
@@ -16776,8 +16743,8 @@
         <v>1558.79</v>
       </c>
     </row>
-    <row r="216" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A216" s="4">
+    <row r="216" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A216" s="3">
         <v>45889</v>
       </c>
       <c r="B216">
@@ -16795,7 +16762,6 @@
       <c r="F216">
         <v>264.35199999999998</v>
       </c>
-      <c r="H216" s="3"/>
       <c r="J216">
         <v>1317.84</v>
       </c>
@@ -16835,7 +16801,7 @@
       <c r="V216">
         <v>74413452</v>
       </c>
-      <c r="W216" s="5">
+      <c r="W216" s="4">
         <v>20.9</v>
       </c>
       <c r="X216">
@@ -16845,8 +16811,8 @@
         <v>1559.74</v>
       </c>
     </row>
-    <row r="217" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A217" s="4">
+    <row r="217" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A217" s="3">
         <v>45890</v>
       </c>
       <c r="B217">
@@ -16864,7 +16830,6 @@
       <c r="F217">
         <v>264.50700000000001</v>
       </c>
-      <c r="H217" s="3"/>
       <c r="J217">
         <v>1329.78</v>
       </c>
@@ -16904,7 +16869,7 @@
       <c r="V217">
         <v>74958568</v>
       </c>
-      <c r="W217" s="5">
+      <c r="W217" s="4">
         <v>20.9</v>
       </c>
       <c r="X217">
@@ -16914,8 +16879,8 @@
         <v>1560.68</v>
       </c>
     </row>
-    <row r="218" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A218" s="4">
+    <row r="218" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A218" s="3">
         <v>45891</v>
       </c>
       <c r="B218">
@@ -16933,7 +16898,6 @@
       <c r="F218">
         <v>266.61700000000002</v>
       </c>
-      <c r="H218" s="3"/>
       <c r="J218">
         <v>1337.23</v>
       </c>
@@ -16973,7 +16937,7 @@
       <c r="V218">
         <v>75688324</v>
       </c>
-      <c r="W218" s="5">
+      <c r="W218" s="4">
         <v>20.9</v>
       </c>
       <c r="X218">
@@ -16983,8 +16947,8 @@
         <v>1561.63</v>
       </c>
     </row>
-    <row r="219" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A219" s="4">
+    <row r="219" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A219" s="3">
         <v>45894</v>
       </c>
       <c r="B219">
@@ -17002,7 +16966,6 @@
       <c r="F219">
         <v>265.59199999999998</v>
       </c>
-      <c r="H219" s="3"/>
       <c r="J219">
         <v>1367.98</v>
       </c>
@@ -17042,7 +17005,7 @@
       <c r="V219">
         <v>74892374</v>
       </c>
-      <c r="W219" s="5">
+      <c r="W219" s="4">
         <v>20.9</v>
       </c>
       <c r="X219">
@@ -17052,8 +17015,8 @@
         <v>1562.58</v>
       </c>
     </row>
-    <row r="220" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A220" s="4">
+    <row r="220" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A220" s="3">
         <v>45895</v>
       </c>
       <c r="B220">
@@ -17071,7 +17034,6 @@
       <c r="F220">
         <v>269.767</v>
       </c>
-      <c r="H220" s="3"/>
       <c r="J220">
         <v>1377.12</v>
       </c>
@@ -17111,7 +17073,7 @@
       <c r="V220">
         <v>75645533</v>
       </c>
-      <c r="W220" s="5">
+      <c r="W220" s="4">
         <v>20.9</v>
       </c>
       <c r="X220">
@@ -17121,8 +17083,8 @@
         <v>1565.43</v>
       </c>
     </row>
-    <row r="221" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A221" s="4">
+    <row r="221" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A221" s="3">
         <v>45896</v>
       </c>
       <c r="B221">
@@ -17140,7 +17102,6 @@
       <c r="F221">
         <v>272.31400000000002</v>
       </c>
-      <c r="H221" s="3"/>
       <c r="J221">
         <v>1370.79</v>
       </c>
@@ -17180,7 +17141,7 @@
       <c r="V221">
         <v>76073256</v>
       </c>
-      <c r="W221" s="5">
+      <c r="W221" s="4">
         <v>20.9</v>
       </c>
       <c r="X221">
@@ -17190,8 +17151,8 @@
         <v>1566.38</v>
       </c>
     </row>
-    <row r="222" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A222" s="4">
+    <row r="222" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A222" s="3">
         <v>45897</v>
       </c>
       <c r="B222">
@@ -17209,7 +17170,6 @@
       <c r="F222">
         <v>270.47699999999998</v>
       </c>
-      <c r="H222" s="3"/>
       <c r="J222">
         <v>1349.44</v>
       </c>
@@ -17249,7 +17209,7 @@
       <c r="V222">
         <v>76445721</v>
       </c>
-      <c r="W222" s="5">
+      <c r="W222" s="4">
         <v>20.9</v>
       </c>
       <c r="X222">
@@ -17259,8 +17219,8 @@
         <v>1567.33</v>
       </c>
     </row>
-    <row r="223" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A223" s="4">
+    <row r="223" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A223" s="3">
         <v>45898</v>
       </c>
       <c r="B223">
@@ -17278,7 +17238,6 @@
       <c r="F223">
         <v>269.37700000000001</v>
       </c>
-      <c r="H223" s="3"/>
       <c r="J223">
         <v>1361.42</v>
       </c>
@@ -17318,7 +17277,7 @@
       <c r="V223">
         <v>76568906</v>
       </c>
-      <c r="W223" s="5">
+      <c r="W223" s="4">
         <v>20.9</v>
       </c>
       <c r="X223">
@@ -17328,8 +17287,8 @@
         <v>1568.28</v>
       </c>
     </row>
-    <row r="224" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A224" s="4">
+    <row r="224" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A224" s="3">
         <v>45901</v>
       </c>
       <c r="B224">
@@ -17338,7 +17297,6 @@
       <c r="C224">
         <v>1939743.31</v>
       </c>
-      <c r="H224" s="3"/>
       <c r="J224">
         <v>1391.88</v>
       </c>
@@ -17382,8 +17340,8 @@
         <v>1569.24</v>
       </c>
     </row>
-    <row r="225" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A225" s="4">
+    <row r="225" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A225" s="3">
         <v>45902</v>
       </c>
       <c r="B225">
@@ -17401,7 +17359,6 @@
       <c r="F225">
         <v>271.22799999999899</v>
       </c>
-      <c r="H225" s="3"/>
       <c r="J225">
         <v>1378.91</v>
       </c>
@@ -17445,8 +17402,8 @@
         <v>1572.1</v>
       </c>
     </row>
-    <row r="226" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A226" s="4">
+    <row r="226" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A226" s="3">
         <v>45903</v>
       </c>
       <c r="B226">
@@ -17464,7 +17421,6 @@
       <c r="F226">
         <v>271.45</v>
       </c>
-      <c r="H226" s="3"/>
       <c r="J226">
         <v>1377.09</v>
       </c>
@@ -17508,8 +17464,8 @@
         <v>1573.05</v>
       </c>
     </row>
-    <row r="227" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A227" s="4">
+    <row r="227" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A227" s="3">
         <v>45904</v>
       </c>
       <c r="B227">
@@ -17527,7 +17483,6 @@
       <c r="F227">
         <v>271.90600000000001</v>
       </c>
-      <c r="H227" s="3"/>
       <c r="J227">
         <v>1382.69</v>
       </c>
@@ -17556,8 +17511,8 @@
         <v>1574.01</v>
       </c>
     </row>
-    <row r="228" spans="1:25" x14ac:dyDescent="0.25">
-      <c r="A228" s="4">
+    <row r="228" spans="1:25" x14ac:dyDescent="0.35">
+      <c r="A228" s="3">
         <v>45905</v>
       </c>
       <c r="B228">
@@ -17566,7 +17521,6 @@
       <c r="C228">
         <v>1997624.37</v>
       </c>
-      <c r="H228" s="3"/>
       <c r="J228">
         <v>1386.8</v>
       </c>
@@ -17577,16 +17531,16 @@
         <v>1574.96</v>
       </c>
     </row>
-    <row r="229" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:25" x14ac:dyDescent="0.35">
       <c r="H229" s="1"/>
     </row>
-    <row r="230" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:25" x14ac:dyDescent="0.35">
       <c r="H230" s="1"/>
     </row>
-    <row r="231" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:25" x14ac:dyDescent="0.35">
       <c r="H231" s="1"/>
     </row>
-    <row r="232" spans="1:25" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:25" x14ac:dyDescent="0.35">
       <c r="H232" s="1"/>
     </row>
   </sheetData>
@@ -17596,15 +17550,15 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D68D9661-D5F8-4698-9487-A24691442B2A}">
-  <dimension ref="A1:E31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.7265625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="23.140625" customWidth="1"/>
-    <col min="4" max="4" width="36.140625" customWidth="1"/>
+    <col min="1" max="1" width="33.1796875" customWidth="1"/>
+    <col min="2" max="3" width="23.1796875" customWidth="1"/>
+    <col min="4" max="4" width="36.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -17621,7 +17575,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -17638,7 +17592,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -17655,7 +17609,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -17672,7 +17626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -17689,7 +17643,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -17706,14 +17660,14 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C7" t="s">
+      <c r="C7" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D7" t="s">
@@ -17723,14 +17677,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A8" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C8" t="s">
+      <c r="C8" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D8" t="s">
@@ -17740,14 +17694,14 @@
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A9" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="C9" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D9" t="s">
@@ -17757,7 +17711,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>30</v>
       </c>
@@ -17774,7 +17728,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>31</v>
       </c>
@@ -17791,7 +17745,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>32</v>
       </c>
@@ -17808,7 +17762,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>33</v>
       </c>
@@ -17825,7 +17779,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>34</v>
       </c>
@@ -17842,7 +17796,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>35</v>
       </c>
@@ -17859,7 +17813,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>36</v>
       </c>
@@ -17876,7 +17830,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>37</v>
       </c>
@@ -17893,7 +17847,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>38</v>
       </c>
@@ -17910,7 +17864,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>39</v>
       </c>
@@ -17927,7 +17881,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>40</v>
       </c>
@@ -17944,7 +17898,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>41</v>
       </c>
@@ -17961,7 +17915,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>42</v>
       </c>
@@ -17978,14 +17932,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B23" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C23" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D23" t="s">
@@ -17995,7 +17949,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>44</v>
       </c>
@@ -18012,7 +17966,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>45</v>
       </c>
@@ -18029,7 +17983,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>70</v>
       </c>
@@ -18042,11 +17996,11 @@
       <c r="D26" t="s">
         <v>71</v>
       </c>
-      <c r="E26" s="7" t="s">
+      <c r="E26" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>72</v>
       </c>
@@ -18063,7 +18017,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>74</v>
       </c>
@@ -18076,18 +18030,18 @@
       <c r="D28" t="s">
         <v>75</v>
       </c>
-      <c r="E28" s="7" t="s">
+      <c r="E28" s="5" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="B29" t="s">
+      <c r="B29" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="C29" t="s">
+      <c r="C29" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D29" t="s">
@@ -18097,14 +18051,14 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="6" t="s">
         <v>80</v>
       </c>
-      <c r="B30" t="s">
+      <c r="B30" s="6" t="s">
         <v>82</v>
       </c>
-      <c r="C30" t="s">
+      <c r="C30" s="6" t="s">
         <v>25</v>
       </c>
       <c r="D30" t="s">
@@ -18114,9 +18068,9 @@
         <v>46</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B31" t="s">
         <v>59</v>
@@ -18125,10 +18079,18 @@
         <v>20</v>
       </c>
       <c r="D31" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="E31" s="2" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>84</v>
+      </c>
+      <c r="C32" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
